--- a/research/traditional_assets/database/data/bulgaria/bulgaria_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_metals_mining.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bul_alcm" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0809</v>
+        <v>0.161</v>
+      </c>
+      <c r="E2">
+        <v>0.11</v>
       </c>
       <c r="G2">
-        <v>0.02888475836431226</v>
+        <v>0.0258028483663781</v>
       </c>
       <c r="H2">
-        <v>0.02888475836431226</v>
+        <v>0.0258028483663781</v>
       </c>
       <c r="I2">
-        <v>-0.008996282527881041</v>
+        <v>0.0298799218095504</v>
       </c>
       <c r="J2">
-        <v>-0.008996282527881041</v>
+        <v>0.02687569054065539</v>
       </c>
       <c r="K2">
-        <v>-1.67</v>
+        <v>16.6</v>
       </c>
       <c r="L2">
-        <v>-0.006208178438661709</v>
+        <v>0.04635576654565764</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.432</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>0.005503184713375796</v>
+        <v>0.02982456140350877</v>
       </c>
       <c r="W2">
-        <v>-0.01356620633631194</v>
+        <v>0.1325878594249201</v>
       </c>
       <c r="X2">
-        <v>0.1209083180926361</v>
+        <v>0.2319181843735395</v>
       </c>
       <c r="Y2">
-        <v>-0.1344745244289481</v>
+        <v>-0.09933032494861935</v>
       </c>
       <c r="Z2">
-        <v>1.371679159655296</v>
+        <v>1.588942627678928</v>
       </c>
       <c r="AA2">
-        <v>-0.01234001325786548</v>
+        <v>0.04270393034835468</v>
       </c>
       <c r="AB2">
-        <v>0.07772565881205383</v>
+        <v>0.1451573895580498</v>
       </c>
       <c r="AC2">
-        <v>-0.09006567206991932</v>
+        <v>-0.1024534592096951</v>
       </c>
       <c r="AD2">
-        <v>76.2</v>
+        <v>88.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>76.2</v>
+        <v>88.7</v>
       </c>
       <c r="AG2">
-        <v>75.768</v>
+        <v>86.32000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.4925662572721397</v>
+        <v>0.5264094955489614</v>
       </c>
       <c r="AI2">
-        <v>0.3761105626850937</v>
+        <v>0.4285024154589372</v>
       </c>
       <c r="AJ2">
-        <v>0.4911452796432183</v>
+        <v>0.5196243679267999</v>
       </c>
       <c r="AK2">
-        <v>0.3747774128447627</v>
+        <v>0.4218551461245235</v>
       </c>
       <c r="AL2">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AM2">
-        <v>1.019</v>
+        <v>1.16</v>
       </c>
       <c r="AN2">
-        <v>8.933177022274327</v>
+        <v>4.369458128078818</v>
       </c>
       <c r="AO2">
-        <v>-2.372549019607843</v>
+        <v>9.224137931034482</v>
       </c>
       <c r="AP2">
-        <v>8.882532239155921</v>
+        <v>4.252216748768473</v>
       </c>
       <c r="AQ2">
-        <v>-2.374877330716388</v>
+        <v>9.224137931034482</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0809</v>
+        <v>0.161</v>
+      </c>
+      <c r="E3">
+        <v>0.11</v>
       </c>
       <c r="G3">
-        <v>0.02888475836431226</v>
+        <v>0.0258028483663781</v>
       </c>
       <c r="H3">
-        <v>0.02888475836431226</v>
+        <v>0.0258028483663781</v>
       </c>
       <c r="I3">
-        <v>-0.008996282527881041</v>
+        <v>0.0298799218095504</v>
       </c>
       <c r="J3">
-        <v>-0.008996282527881041</v>
+        <v>0.02687569054065539</v>
       </c>
       <c r="K3">
-        <v>-1.67</v>
+        <v>16.6</v>
       </c>
       <c r="L3">
-        <v>-0.006208178438661709</v>
+        <v>0.04635576654565764</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.432</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>0.005503184713375796</v>
+        <v>0.02982456140350877</v>
       </c>
       <c r="W3">
-        <v>-0.01356620633631194</v>
+        <v>0.1325878594249201</v>
       </c>
       <c r="X3">
-        <v>0.1209083180926361</v>
+        <v>0.2319181843735395</v>
       </c>
       <c r="Y3">
-        <v>-0.1344745244289481</v>
+        <v>-0.09933032494861935</v>
       </c>
       <c r="Z3">
-        <v>1.371679159655296</v>
+        <v>1.588942627678928</v>
       </c>
       <c r="AA3">
-        <v>-0.01234001325786548</v>
+        <v>0.04270393034835468</v>
       </c>
       <c r="AB3">
-        <v>0.07772565881205383</v>
+        <v>0.1451573895580498</v>
       </c>
       <c r="AC3">
-        <v>-0.09006567206991932</v>
+        <v>-0.1024534592096951</v>
       </c>
       <c r="AD3">
-        <v>76.2</v>
+        <v>88.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>76.2</v>
+        <v>88.7</v>
       </c>
       <c r="AG3">
-        <v>75.768</v>
+        <v>86.32000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.4925662572721397</v>
+        <v>0.5264094955489614</v>
       </c>
       <c r="AI3">
-        <v>0.3761105626850937</v>
+        <v>0.4285024154589372</v>
       </c>
       <c r="AJ3">
-        <v>0.4911452796432183</v>
+        <v>0.5196243679267999</v>
       </c>
       <c r="AK3">
-        <v>0.3747774128447627</v>
+        <v>0.4218551461245235</v>
       </c>
       <c r="AL3">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AM3">
-        <v>1.019</v>
+        <v>1.16</v>
       </c>
       <c r="AN3">
-        <v>8.933177022274327</v>
+        <v>4.369458128078818</v>
       </c>
       <c r="AO3">
-        <v>-2.372549019607843</v>
+        <v>9.224137931034482</v>
       </c>
       <c r="AP3">
-        <v>8.882532239155921</v>
+        <v>4.252216748768473</v>
       </c>
       <c r="AQ3">
-        <v>-2.374877330716388</v>
+        <v>9.224137931034482</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alcomet AD (BUL:ALCM)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUL:ALCM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.526409495548961</v>
+      </c>
+      <c r="F2">
+        <v>0.13</v>
+      </c>
+      <c r="G2">
+        <v>79.8</v>
+      </c>
+      <c r="H2">
+        <v>164.948011363393</v>
+      </c>
+      <c r="I2">
+        <v>166.12</v>
+      </c>
+      <c r="J2">
+        <v>184.473011363393</v>
+      </c>
+      <c r="K2">
+        <v>88.7</v>
+      </c>
+      <c r="L2">
+        <v>21.905</v>
+      </c>
+      <c r="M2">
+        <v>0.14515738955805</v>
+      </c>
+      <c r="N2">
+        <v>0.13457601310242</v>
+      </c>
+      <c r="O2">
+        <v>0.06710201834862391</v>
+      </c>
+      <c r="P2">
+        <v>0.04257</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.231918184373539</v>
+      </c>
+      <c r="T2">
+        <v>0.148324038048759</v>
+      </c>
+      <c r="U2">
+        <v>2.22663096071827</v>
+      </c>
+      <c r="V2">
+        <v>1.26279984898028</v>
+      </c>
+      <c r="W2">
+        <v>10.32712370784277</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>79.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.07455779816513761</v>
+      </c>
+      <c r="AD2">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>20.3</v>
+      </c>
+      <c r="AH2">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>19.6</v>
+      </c>
+      <c r="AJ2">
+        <v>88.7</v>
+      </c>
+      <c r="AK2">
+        <v>88.7</v>
+      </c>
+      <c r="AL2">
+        <v>1.16</v>
+      </c>
+      <c r="AM2">
+        <v>88.7</v>
+      </c>
+      <c r="AN2">
+        <v>2.38</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.135340945392523</v>
+      </c>
+      <c r="C2">
+        <v>185.3913583572966</v>
+      </c>
+      <c r="D2">
+        <v>183.0113583572966</v>
+      </c>
+      <c r="E2">
+        <v>-88.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.38</v>
+      </c>
+      <c r="H2">
+        <v>79.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>20.3</v>
+      </c>
+      <c r="K2">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L2">
+        <v>10.7</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>10.7</v>
+      </c>
+      <c r="O2">
+        <v>1.07</v>
+      </c>
+      <c r="P2">
+        <v>9.629999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>19.23</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.135340945392523</v>
+      </c>
+      <c r="T2">
+        <v>1.113106249861041</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W2">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1352677044471305</v>
+      </c>
+      <c r="C3">
+        <v>183.8453056348386</v>
+      </c>
+      <c r="D3">
+        <v>183.1503056348386</v>
+      </c>
+      <c r="E3">
+        <v>-87.015</v>
+      </c>
+      <c r="F3">
+        <v>1.685</v>
+      </c>
+      <c r="G3">
+        <v>2.38</v>
+      </c>
+      <c r="H3">
+        <v>79.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>20.3</v>
+      </c>
+      <c r="K3">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L3">
+        <v>10.7</v>
+      </c>
+      <c r="M3">
+        <v>0.0770045</v>
+      </c>
+      <c r="N3">
+        <v>10.6229955</v>
+      </c>
+      <c r="O3">
+        <v>1.06229955</v>
+      </c>
+      <c r="P3">
+        <v>9.560695949999999</v>
+      </c>
+      <c r="Q3">
+        <v>19.16069595</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1362185903506369</v>
+      </c>
+      <c r="T3">
+        <v>1.12322539758705</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W3">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>138.9529183359414</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.135194463501738</v>
+      </c>
+      <c r="C4">
+        <v>182.2994640579091</v>
+      </c>
+      <c r="D4">
+        <v>183.2894640579091</v>
+      </c>
+      <c r="E4">
+        <v>-85.33</v>
+      </c>
+      <c r="F4">
+        <v>3.37</v>
+      </c>
+      <c r="G4">
+        <v>2.38</v>
+      </c>
+      <c r="H4">
+        <v>79.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>20.3</v>
+      </c>
+      <c r="K4">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L4">
+        <v>10.7</v>
+      </c>
+      <c r="M4">
+        <v>0.154009</v>
+      </c>
+      <c r="N4">
+        <v>10.545991</v>
+      </c>
+      <c r="O4">
+        <v>1.0545991</v>
+      </c>
+      <c r="P4">
+        <v>9.4913919</v>
+      </c>
+      <c r="Q4">
+        <v>19.0913919</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1371141464303449</v>
+      </c>
+      <c r="T4">
+        <v>1.133551058531958</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W4">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>69.47645916797069</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1351212225563454</v>
+      </c>
+      <c r="C5">
+        <v>180.7538341081619</v>
+      </c>
+      <c r="D5">
+        <v>183.4288341081619</v>
+      </c>
+      <c r="E5">
+        <v>-83.64500000000001</v>
+      </c>
+      <c r="F5">
+        <v>5.055</v>
+      </c>
+      <c r="G5">
+        <v>2.38</v>
+      </c>
+      <c r="H5">
+        <v>79.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>20.3</v>
+      </c>
+      <c r="K5">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L5">
+        <v>10.7</v>
+      </c>
+      <c r="M5">
+        <v>0.2310135</v>
+      </c>
+      <c r="N5">
+        <v>10.4689865</v>
+      </c>
+      <c r="O5">
+        <v>1.04689865</v>
+      </c>
+      <c r="P5">
+        <v>9.42208785</v>
+      </c>
+      <c r="Q5">
+        <v>19.02208785</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1380281675838613</v>
+      </c>
+      <c r="T5">
+        <v>1.144089619702533</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W5">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>46.3176394453138</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.135047981610953</v>
+      </c>
+      <c r="C6">
+        <v>179.2084162687169</v>
+      </c>
+      <c r="D6">
+        <v>183.568416268717</v>
+      </c>
+      <c r="E6">
+        <v>-81.96000000000001</v>
+      </c>
+      <c r="F6">
+        <v>6.74</v>
+      </c>
+      <c r="G6">
+        <v>2.38</v>
+      </c>
+      <c r="H6">
+        <v>79.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>20.3</v>
+      </c>
+      <c r="K6">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L6">
+        <v>10.7</v>
+      </c>
+      <c r="M6">
+        <v>0.308018</v>
+      </c>
+      <c r="N6">
+        <v>10.391982</v>
+      </c>
+      <c r="O6">
+        <v>1.0391982</v>
+      </c>
+      <c r="P6">
+        <v>9.352783799999999</v>
+      </c>
+      <c r="Q6">
+        <v>18.9527838</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1389612308447427</v>
+      </c>
+      <c r="T6">
+        <v>1.15484773423083</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W6">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>34.73822958398534</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1349747406655604</v>
+      </c>
+      <c r="C7">
+        <v>177.6632110241662</v>
+      </c>
+      <c r="D7">
+        <v>183.7082110241662</v>
+      </c>
+      <c r="E7">
+        <v>-80.27500000000001</v>
+      </c>
+      <c r="F7">
+        <v>8.425000000000001</v>
+      </c>
+      <c r="G7">
+        <v>2.38</v>
+      </c>
+      <c r="H7">
+        <v>79.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>20.3</v>
+      </c>
+      <c r="K7">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L7">
+        <v>10.7</v>
+      </c>
+      <c r="M7">
+        <v>0.3850225</v>
+      </c>
+      <c r="N7">
+        <v>10.3149775</v>
+      </c>
+      <c r="O7">
+        <v>1.03149775</v>
+      </c>
+      <c r="P7">
+        <v>9.28347975</v>
+      </c>
+      <c r="Q7">
+        <v>18.88347975</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1399139375426952</v>
+      </c>
+      <c r="T7">
+        <v>1.165832335380774</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W7">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>27.79058366718828</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1349014997201679</v>
+      </c>
+      <c r="C8">
+        <v>176.1182188605783</v>
+      </c>
+      <c r="D8">
+        <v>183.8482188605783</v>
+      </c>
+      <c r="E8">
+        <v>-78.59</v>
+      </c>
+      <c r="F8">
+        <v>10.11</v>
+      </c>
+      <c r="G8">
+        <v>2.38</v>
+      </c>
+      <c r="H8">
+        <v>79.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>20.3</v>
+      </c>
+      <c r="K8">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L8">
+        <v>10.7</v>
+      </c>
+      <c r="M8">
+        <v>0.462027</v>
+      </c>
+      <c r="N8">
+        <v>10.237973</v>
+      </c>
+      <c r="O8">
+        <v>1.0237973</v>
+      </c>
+      <c r="P8">
+        <v>9.214175699999998</v>
+      </c>
+      <c r="Q8">
+        <v>18.8141757</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1408869145959233</v>
+      </c>
+      <c r="T8">
+        <v>1.177050651448803</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W8">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>23.1588197226569</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1348282587747754</v>
+      </c>
+      <c r="C9">
+        <v>174.5734402655052</v>
+      </c>
+      <c r="D9">
+        <v>183.9884402655052</v>
+      </c>
+      <c r="E9">
+        <v>-76.905</v>
+      </c>
+      <c r="F9">
+        <v>11.795</v>
+      </c>
+      <c r="G9">
+        <v>2.38</v>
+      </c>
+      <c r="H9">
+        <v>79.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>20.3</v>
+      </c>
+      <c r="K9">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L9">
+        <v>10.7</v>
+      </c>
+      <c r="M9">
+        <v>0.5390315000000001</v>
+      </c>
+      <c r="N9">
+        <v>10.1609685</v>
+      </c>
+      <c r="O9">
+        <v>1.01609685</v>
+      </c>
+      <c r="P9">
+        <v>9.144871649999999</v>
+      </c>
+      <c r="Q9">
+        <v>18.74487165</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1418808158868552</v>
+      </c>
+      <c r="T9">
+        <v>1.188510221625821</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W9">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>19.85041690513448</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1347550178293828</v>
+      </c>
+      <c r="C10">
+        <v>173.0288757279872</v>
+      </c>
+      <c r="D10">
+        <v>184.1288757279872</v>
+      </c>
+      <c r="E10">
+        <v>-75.22</v>
+      </c>
+      <c r="F10">
+        <v>13.48</v>
+      </c>
+      <c r="G10">
+        <v>2.38</v>
+      </c>
+      <c r="H10">
+        <v>79.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>20.3</v>
+      </c>
+      <c r="K10">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L10">
+        <v>10.7</v>
+      </c>
+      <c r="M10">
+        <v>0.616036</v>
+      </c>
+      <c r="N10">
+        <v>10.083964</v>
+      </c>
+      <c r="O10">
+        <v>1.0083964</v>
+      </c>
+      <c r="P10">
+        <v>9.075567599999999</v>
+      </c>
+      <c r="Q10">
+        <v>18.6755676</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.14289632372759</v>
+      </c>
+      <c r="T10">
+        <v>1.200218912893644</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W10">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>17.36911479199268</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1346817768839903</v>
+      </c>
+      <c r="C11">
+        <v>171.484525738559</v>
+      </c>
+      <c r="D11">
+        <v>184.269525738559</v>
+      </c>
+      <c r="E11">
+        <v>-73.535</v>
+      </c>
+      <c r="F11">
+        <v>15.165</v>
+      </c>
+      <c r="G11">
+        <v>2.38</v>
+      </c>
+      <c r="H11">
+        <v>79.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>20.3</v>
+      </c>
+      <c r="K11">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L11">
+        <v>10.7</v>
+      </c>
+      <c r="M11">
+        <v>0.6930405000000001</v>
+      </c>
+      <c r="N11">
+        <v>10.0069595</v>
+      </c>
+      <c r="O11">
+        <v>1.00069595</v>
+      </c>
+      <c r="P11">
+        <v>9.00626355</v>
+      </c>
+      <c r="Q11">
+        <v>18.60626355</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1439341504219674</v>
+      </c>
+      <c r="T11">
+        <v>1.212184938035485</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W11">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>15.43921314843793</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1346085359385978</v>
+      </c>
+      <c r="C12">
+        <v>169.9403907892552</v>
+      </c>
+      <c r="D12">
+        <v>184.4103907892552</v>
+      </c>
+      <c r="E12">
+        <v>-71.84999999999999</v>
+      </c>
+      <c r="F12">
+        <v>16.85</v>
+      </c>
+      <c r="G12">
+        <v>2.38</v>
+      </c>
+      <c r="H12">
+        <v>79.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>20.3</v>
+      </c>
+      <c r="K12">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L12">
+        <v>10.7</v>
+      </c>
+      <c r="M12">
+        <v>0.7700450000000001</v>
+      </c>
+      <c r="N12">
+        <v>9.929955</v>
+      </c>
+      <c r="O12">
+        <v>0.9929954999999997</v>
+      </c>
+      <c r="P12">
+        <v>8.9369595</v>
+      </c>
+      <c r="Q12">
+        <v>18.5369595</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1449950399317753</v>
+      </c>
+      <c r="T12">
+        <v>1.224416874847145</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W12">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>13.89529183359414</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1346936949932053</v>
+      </c>
+      <c r="C13">
+        <v>168.0916238748557</v>
+      </c>
+      <c r="D13">
+        <v>184.2466238748557</v>
+      </c>
+      <c r="E13">
+        <v>-70.16500000000001</v>
+      </c>
+      <c r="F13">
+        <v>18.535</v>
+      </c>
+      <c r="G13">
+        <v>2.38</v>
+      </c>
+      <c r="H13">
+        <v>79.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>20.3</v>
+      </c>
+      <c r="K13">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L13">
+        <v>10.7</v>
+      </c>
+      <c r="M13">
+        <v>0.8767055</v>
+      </c>
+      <c r="N13">
+        <v>9.823294499999999</v>
+      </c>
+      <c r="O13">
+        <v>0.9823294499999997</v>
+      </c>
+      <c r="P13">
+        <v>8.840965049999999</v>
+      </c>
+      <c r="Q13">
+        <v>18.44096505</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1460797696552868</v>
+      </c>
+      <c r="T13">
+        <v>1.236923686643336</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W13">
+        <v>0.04257</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>12.20478256381419</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1346348540478128</v>
+      </c>
+      <c r="C14">
+        <v>166.5197481201199</v>
+      </c>
+      <c r="D14">
+        <v>184.3597481201199</v>
+      </c>
+      <c r="E14">
+        <v>-68.48</v>
+      </c>
+      <c r="F14">
+        <v>20.22</v>
+      </c>
+      <c r="G14">
+        <v>2.38</v>
+      </c>
+      <c r="H14">
+        <v>79.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>20.3</v>
+      </c>
+      <c r="K14">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L14">
+        <v>10.7</v>
+      </c>
+      <c r="M14">
+        <v>0.956406</v>
+      </c>
+      <c r="N14">
+        <v>9.743594</v>
+      </c>
+      <c r="O14">
+        <v>0.9743593999999998</v>
+      </c>
+      <c r="P14">
+        <v>8.769234600000001</v>
+      </c>
+      <c r="Q14">
+        <v>18.3692346</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.14718915232706</v>
+      </c>
+      <c r="T14">
+        <v>1.249714744162169</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W14">
+        <v>0.04257</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>11.18771735016301</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1345760131024202</v>
+      </c>
+      <c r="C15">
+        <v>164.9480113633928</v>
+      </c>
+      <c r="D15">
+        <v>184.4730113633928</v>
+      </c>
+      <c r="E15">
+        <v>-66.795</v>
+      </c>
+      <c r="F15">
+        <v>21.905</v>
+      </c>
+      <c r="G15">
+        <v>2.38</v>
+      </c>
+      <c r="H15">
+        <v>79.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>20.3</v>
+      </c>
+      <c r="K15">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L15">
+        <v>10.7</v>
+      </c>
+      <c r="M15">
+        <v>1.0361065</v>
+      </c>
+      <c r="N15">
+        <v>9.663893499999999</v>
+      </c>
+      <c r="O15">
+        <v>0.9663893499999996</v>
+      </c>
+      <c r="P15">
+        <v>8.697504149999999</v>
+      </c>
+      <c r="Q15">
+        <v>18.29750415</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1483240380487589</v>
+      </c>
+      <c r="T15">
+        <v>1.262799848980284</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W15">
+        <v>0.04257</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>10.32712370784277</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1349959721570277</v>
+      </c>
+      <c r="C16">
+        <v>162.457664635088</v>
+      </c>
+      <c r="D16">
+        <v>183.667664635088</v>
+      </c>
+      <c r="E16">
+        <v>-65.11</v>
+      </c>
+      <c r="F16">
+        <v>23.59</v>
+      </c>
+      <c r="G16">
+        <v>2.38</v>
+      </c>
+      <c r="H16">
+        <v>79.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>20.3</v>
+      </c>
+      <c r="K16">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L16">
+        <v>10.7</v>
+      </c>
+      <c r="M16">
+        <v>1.205449</v>
+      </c>
+      <c r="N16">
+        <v>9.494551</v>
+      </c>
+      <c r="O16">
+        <v>0.9494550999999998</v>
+      </c>
+      <c r="P16">
+        <v>8.5450959</v>
+      </c>
+      <c r="Q16">
+        <v>18.1450959</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1494853164616601</v>
+      </c>
+      <c r="T16">
+        <v>1.276189258561612</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W16">
+        <v>0.04599</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.876360592609061</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1349713312116352</v>
+      </c>
+      <c r="C17">
+        <v>160.8197238245328</v>
+      </c>
+      <c r="D17">
+        <v>183.7147238245328</v>
+      </c>
+      <c r="E17">
+        <v>-63.425</v>
+      </c>
+      <c r="F17">
+        <v>25.275</v>
+      </c>
+      <c r="G17">
+        <v>2.38</v>
+      </c>
+      <c r="H17">
+        <v>79.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>20.3</v>
+      </c>
+      <c r="K17">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L17">
+        <v>10.7</v>
+      </c>
+      <c r="M17">
+        <v>1.2915525</v>
+      </c>
+      <c r="N17">
+        <v>9.408447499999999</v>
+      </c>
+      <c r="O17">
+        <v>0.9408447499999998</v>
+      </c>
+      <c r="P17">
+        <v>8.467602749999999</v>
+      </c>
+      <c r="Q17">
+        <v>18.06760275</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.150673919072512</v>
+      </c>
+      <c r="T17">
+        <v>1.289893713074265</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W17">
+        <v>0.04599</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.284603219768456</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1352202902662427</v>
+      </c>
+      <c r="C18">
+        <v>158.660368853867</v>
+      </c>
+      <c r="D18">
+        <v>183.240368853867</v>
+      </c>
+      <c r="E18">
+        <v>-61.74</v>
+      </c>
+      <c r="F18">
+        <v>26.96</v>
+      </c>
+      <c r="G18">
+        <v>2.38</v>
+      </c>
+      <c r="H18">
+        <v>79.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>20.3</v>
+      </c>
+      <c r="K18">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L18">
+        <v>10.7</v>
+      </c>
+      <c r="M18">
+        <v>1.42888</v>
+      </c>
+      <c r="N18">
+        <v>9.27112</v>
+      </c>
+      <c r="O18">
+        <v>0.9271119999999998</v>
+      </c>
+      <c r="P18">
+        <v>8.344008000000001</v>
+      </c>
+      <c r="Q18">
+        <v>17.944008</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.151890821745527</v>
+      </c>
+      <c r="T18">
+        <v>1.303924464122934</v>
+      </c>
+      <c r="U18">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W18">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.488382509377973</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1352127493208501</v>
+      </c>
+      <c r="C19">
+        <v>156.9897010415182</v>
+      </c>
+      <c r="D19">
+        <v>183.2547010415182</v>
+      </c>
+      <c r="E19">
+        <v>-60.055</v>
+      </c>
+      <c r="F19">
+        <v>28.645</v>
+      </c>
+      <c r="G19">
+        <v>2.38</v>
+      </c>
+      <c r="H19">
+        <v>79.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>20.3</v>
+      </c>
+      <c r="K19">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L19">
+        <v>10.7</v>
+      </c>
+      <c r="M19">
+        <v>1.518185</v>
+      </c>
+      <c r="N19">
+        <v>9.181814999999999</v>
+      </c>
+      <c r="O19">
+        <v>0.9181814999999997</v>
+      </c>
+      <c r="P19">
+        <v>8.263633499999999</v>
+      </c>
+      <c r="Q19">
+        <v>17.8636335</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1531370473745182</v>
+      </c>
+      <c r="T19">
+        <v>1.318293305558317</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W19">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.047889420591033</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1352052083754576</v>
+      </c>
+      <c r="C20">
+        <v>155.3190354713354</v>
+      </c>
+      <c r="D20">
+        <v>183.2690354713355</v>
+      </c>
+      <c r="E20">
+        <v>-58.37</v>
+      </c>
+      <c r="F20">
+        <v>30.33</v>
+      </c>
+      <c r="G20">
+        <v>2.38</v>
+      </c>
+      <c r="H20">
+        <v>79.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>20.3</v>
+      </c>
+      <c r="K20">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L20">
+        <v>10.7</v>
+      </c>
+      <c r="M20">
+        <v>1.60749</v>
+      </c>
+      <c r="N20">
+        <v>9.092509999999999</v>
+      </c>
+      <c r="O20">
+        <v>0.9092509999999997</v>
+      </c>
+      <c r="P20">
+        <v>8.183259</v>
+      </c>
+      <c r="Q20">
+        <v>17.783259</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1544136687505581</v>
+      </c>
+      <c r="T20">
+        <v>1.333012606540905</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W20">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.656340008335976</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1351976674300651</v>
+      </c>
+      <c r="C21">
+        <v>153.648372143845</v>
+      </c>
+      <c r="D21">
+        <v>183.283372143845</v>
+      </c>
+      <c r="E21">
+        <v>-56.685</v>
+      </c>
+      <c r="F21">
+        <v>32.015</v>
+      </c>
+      <c r="G21">
+        <v>2.38</v>
+      </c>
+      <c r="H21">
+        <v>79.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>20.3</v>
+      </c>
+      <c r="K21">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L21">
+        <v>10.7</v>
+      </c>
+      <c r="M21">
+        <v>1.696795</v>
+      </c>
+      <c r="N21">
+        <v>9.003204999999999</v>
+      </c>
+      <c r="O21">
+        <v>0.9003204999999997</v>
+      </c>
+      <c r="P21">
+        <v>8.1028845</v>
+      </c>
+      <c r="Q21">
+        <v>17.7028845</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1557218116420557</v>
+      </c>
+      <c r="T21">
+        <v>1.348095347053927</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W21">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.306006323686714</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1355501264846726</v>
+      </c>
+      <c r="C22">
+        <v>151.295673956584</v>
+      </c>
+      <c r="D22">
+        <v>182.615673956584</v>
+      </c>
+      <c r="E22">
+        <v>-55</v>
+      </c>
+      <c r="F22">
+        <v>33.7</v>
+      </c>
+      <c r="G22">
+        <v>2.38</v>
+      </c>
+      <c r="H22">
+        <v>79.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>20.3</v>
+      </c>
+      <c r="K22">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L22">
+        <v>10.7</v>
+      </c>
+      <c r="M22">
+        <v>1.8535</v>
+      </c>
+      <c r="N22">
+        <v>8.846499999999999</v>
+      </c>
+      <c r="O22">
+        <v>0.8846499999999997</v>
+      </c>
+      <c r="P22">
+        <v>7.961849999999999</v>
+      </c>
+      <c r="Q22">
+        <v>17.56185</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1570626581058407</v>
+      </c>
+      <c r="T22">
+        <v>1.363555156079775</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W22">
+        <v>0.0495</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.77286215268411</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.13556058553928</v>
+      </c>
+      <c r="C23">
+        <v>149.5909346454229</v>
+      </c>
+      <c r="D23">
+        <v>182.5959346454229</v>
+      </c>
+      <c r="E23">
+        <v>-53.315</v>
+      </c>
+      <c r="F23">
+        <v>35.385</v>
+      </c>
+      <c r="G23">
+        <v>2.38</v>
+      </c>
+      <c r="H23">
+        <v>79.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>20.3</v>
+      </c>
+      <c r="K23">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L23">
+        <v>10.7</v>
+      </c>
+      <c r="M23">
+        <v>1.946175</v>
+      </c>
+      <c r="N23">
+        <v>8.753824999999999</v>
+      </c>
+      <c r="O23">
+        <v>0.8753824999999997</v>
+      </c>
+      <c r="P23">
+        <v>7.878442499999999</v>
+      </c>
+      <c r="Q23">
+        <v>17.4784425</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1584374500497216</v>
+      </c>
+      <c r="T23">
+        <v>1.379406352675897</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W23">
+        <v>0.0495</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.497963954937248</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1355710445938876</v>
+      </c>
+      <c r="C24">
+        <v>147.8861996011275</v>
+      </c>
+      <c r="D24">
+        <v>182.5761996011275</v>
+      </c>
+      <c r="E24">
+        <v>-51.63</v>
+      </c>
+      <c r="F24">
+        <v>37.07</v>
+      </c>
+      <c r="G24">
+        <v>2.38</v>
+      </c>
+      <c r="H24">
+        <v>79.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>20.3</v>
+      </c>
+      <c r="K24">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L24">
+        <v>10.7</v>
+      </c>
+      <c r="M24">
+        <v>2.03885</v>
+      </c>
+      <c r="N24">
+        <v>8.661149999999999</v>
+      </c>
+      <c r="O24">
+        <v>0.8661149999999997</v>
+      </c>
+      <c r="P24">
+        <v>7.795034999999999</v>
+      </c>
+      <c r="Q24">
+        <v>17.395035</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1598474930690866</v>
+      </c>
+      <c r="T24">
+        <v>1.395663990210382</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W24">
+        <v>0.0495</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.2480565024401</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.135581503648495</v>
+      </c>
+      <c r="C25">
+        <v>146.1814688223148</v>
+      </c>
+      <c r="D25">
+        <v>182.5564688223148</v>
+      </c>
+      <c r="E25">
+        <v>-49.945</v>
+      </c>
+      <c r="F25">
+        <v>38.755</v>
+      </c>
+      <c r="G25">
+        <v>2.38</v>
+      </c>
+      <c r="H25">
+        <v>79.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>20.3</v>
+      </c>
+      <c r="K25">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L25">
+        <v>10.7</v>
+      </c>
+      <c r="M25">
+        <v>2.131525</v>
+      </c>
+      <c r="N25">
+        <v>8.568474999999999</v>
+      </c>
+      <c r="O25">
+        <v>0.8568474999999998</v>
+      </c>
+      <c r="P25">
+        <v>7.7116275</v>
+      </c>
+      <c r="Q25">
+        <v>17.3116275</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.161294160582461</v>
+      </c>
+      <c r="T25">
+        <v>1.412343904044463</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W25">
+        <v>0.0495</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.019880132768791</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1355919627031025</v>
+      </c>
+      <c r="C26">
+        <v>144.4767423076019</v>
+      </c>
+      <c r="D26">
+        <v>182.5367423076019</v>
+      </c>
+      <c r="E26">
+        <v>-48.26000000000001</v>
+      </c>
+      <c r="F26">
+        <v>40.44</v>
+      </c>
+      <c r="G26">
+        <v>2.38</v>
+      </c>
+      <c r="H26">
+        <v>79.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>20.3</v>
+      </c>
+      <c r="K26">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L26">
+        <v>10.7</v>
+      </c>
+      <c r="M26">
+        <v>2.2242</v>
+      </c>
+      <c r="N26">
+        <v>8.4758</v>
+      </c>
+      <c r="O26">
+        <v>0.8475799999999998</v>
+      </c>
+      <c r="P26">
+        <v>7.62822</v>
+      </c>
+      <c r="Q26">
+        <v>17.22822</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1627788982935559</v>
+      </c>
+      <c r="T26">
+        <v>1.429462762979442</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W26">
+        <v>0.0495</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.810718460570093</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.13560242175771</v>
+      </c>
+      <c r="C27">
+        <v>142.7720200556065</v>
+      </c>
+      <c r="D27">
+        <v>182.5170200556065</v>
+      </c>
+      <c r="E27">
+        <v>-46.575</v>
+      </c>
+      <c r="F27">
+        <v>42.125</v>
+      </c>
+      <c r="G27">
+        <v>2.38</v>
+      </c>
+      <c r="H27">
+        <v>79.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>20.3</v>
+      </c>
+      <c r="K27">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L27">
+        <v>10.7</v>
+      </c>
+      <c r="M27">
+        <v>2.316875</v>
+      </c>
+      <c r="N27">
+        <v>8.383125</v>
+      </c>
+      <c r="O27">
+        <v>0.8383124999999998</v>
+      </c>
+      <c r="P27">
+        <v>7.5448125</v>
+      </c>
+      <c r="Q27">
+        <v>17.1448125</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1643032290102799</v>
+      </c>
+      <c r="T27">
+        <v>1.447038124819353</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W27">
+        <v>0.0495</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.618289722147289</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1365020808123174</v>
+      </c>
+      <c r="C28">
+        <v>139.4063691590465</v>
+      </c>
+      <c r="D28">
+        <v>180.8363691590465</v>
+      </c>
+      <c r="E28">
+        <v>-44.89</v>
+      </c>
+      <c r="F28">
+        <v>43.81</v>
+      </c>
+      <c r="G28">
+        <v>2.38</v>
+      </c>
+      <c r="H28">
+        <v>79.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>20.3</v>
+      </c>
+      <c r="K28">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L28">
+        <v>10.7</v>
+      </c>
+      <c r="M28">
+        <v>2.576028</v>
+      </c>
+      <c r="N28">
+        <v>8.123971999999998</v>
+      </c>
+      <c r="O28">
+        <v>0.8123971999999997</v>
+      </c>
+      <c r="P28">
+        <v>7.311574799999999</v>
+      </c>
+      <c r="Q28">
+        <v>16.9115748</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.165868757854483</v>
+      </c>
+      <c r="T28">
+        <v>1.465088496438721</v>
+      </c>
+      <c r="U28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W28">
+        <v>0.05292000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.153681559361932</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1375673398669249</v>
+      </c>
+      <c r="C29">
+        <v>135.7709513396684</v>
+      </c>
+      <c r="D29">
+        <v>178.8859513396684</v>
+      </c>
+      <c r="E29">
+        <v>-43.205</v>
+      </c>
+      <c r="F29">
+        <v>45.495</v>
+      </c>
+      <c r="G29">
+        <v>2.38</v>
+      </c>
+      <c r="H29">
+        <v>79.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>20.3</v>
+      </c>
+      <c r="K29">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L29">
+        <v>10.7</v>
+      </c>
+      <c r="M29">
+        <v>2.866185</v>
+      </c>
+      <c r="N29">
+        <v>7.833815</v>
+      </c>
+      <c r="O29">
+        <v>0.7833814999999997</v>
+      </c>
+      <c r="P29">
+        <v>7.0504335</v>
+      </c>
+      <c r="Q29">
+        <v>16.6504335</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1674771778998972</v>
+      </c>
+      <c r="T29">
+        <v>1.483633398787387</v>
+      </c>
+      <c r="U29">
+        <v>0.063</v>
+      </c>
+      <c r="V29">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W29">
+        <v>0.0567</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>3.733185401500601</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1376497989215324</v>
+      </c>
+      <c r="C30">
+        <v>133.9367272988412</v>
+      </c>
+      <c r="D30">
+        <v>178.7367272988412</v>
+      </c>
+      <c r="E30">
+        <v>-41.52</v>
+      </c>
+      <c r="F30">
+        <v>47.18000000000001</v>
+      </c>
+      <c r="G30">
+        <v>2.38</v>
+      </c>
+      <c r="H30">
+        <v>79.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>20.3</v>
+      </c>
+      <c r="K30">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L30">
+        <v>10.7</v>
+      </c>
+      <c r="M30">
+        <v>2.97234</v>
+      </c>
+      <c r="N30">
+        <v>7.727659999999998</v>
+      </c>
+      <c r="O30">
+        <v>0.7727659999999996</v>
+      </c>
+      <c r="P30">
+        <v>6.954893999999999</v>
+      </c>
+      <c r="Q30">
+        <v>16.554894</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1691302762799061</v>
+      </c>
+      <c r="T30">
+        <v>1.502693437312405</v>
+      </c>
+      <c r="U30">
+        <v>0.063</v>
+      </c>
+      <c r="V30">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W30">
+        <v>0.0567</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.599857351447007</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1395853579761399</v>
+      </c>
+      <c r="C31">
+        <v>128.8191305619613</v>
+      </c>
+      <c r="D31">
+        <v>175.3041305619613</v>
+      </c>
+      <c r="E31">
+        <v>-39.83500000000001</v>
+      </c>
+      <c r="F31">
+        <v>48.86499999999999</v>
+      </c>
+      <c r="G31">
+        <v>2.38</v>
+      </c>
+      <c r="H31">
+        <v>79.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>20.3</v>
+      </c>
+      <c r="K31">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L31">
+        <v>10.7</v>
+      </c>
+      <c r="M31">
+        <v>3.4254365</v>
+      </c>
+      <c r="N31">
+        <v>7.274563499999999</v>
+      </c>
+      <c r="O31">
+        <v>0.7274563499999998</v>
+      </c>
+      <c r="P31">
+        <v>6.54710715</v>
+      </c>
+      <c r="Q31">
+        <v>16.14710715</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1708299408114646</v>
+      </c>
+      <c r="T31">
+        <v>1.522290378331085</v>
+      </c>
+      <c r="U31">
+        <v>0.0701</v>
+      </c>
+      <c r="V31">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W31">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.123689491835566</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1397317170307473</v>
+      </c>
+      <c r="C32">
+        <v>126.8799255650323</v>
+      </c>
+      <c r="D32">
+        <v>175.0499255650323</v>
+      </c>
+      <c r="E32">
+        <v>-38.15000000000001</v>
+      </c>
+      <c r="F32">
+        <v>50.55</v>
+      </c>
+      <c r="G32">
+        <v>2.38</v>
+      </c>
+      <c r="H32">
+        <v>79.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>20.3</v>
+      </c>
+      <c r="K32">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L32">
+        <v>10.7</v>
+      </c>
+      <c r="M32">
+        <v>3.543555</v>
+      </c>
+      <c r="N32">
+        <v>7.156445</v>
+      </c>
+      <c r="O32">
+        <v>0.7156444999999998</v>
+      </c>
+      <c r="P32">
+        <v>6.4408005</v>
+      </c>
+      <c r="Q32">
+        <v>16.0408005</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1725781671867819</v>
+      </c>
+      <c r="T32">
+        <v>1.542447231950299</v>
+      </c>
+      <c r="U32">
+        <v>0.0701</v>
+      </c>
+      <c r="V32">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W32">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.019566508774381</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1458207760853548</v>
+      </c>
+      <c r="C33">
+        <v>115.2352768570093</v>
+      </c>
+      <c r="D33">
+        <v>165.0902768570093</v>
+      </c>
+      <c r="E33">
+        <v>-36.465</v>
+      </c>
+      <c r="F33">
+        <v>52.235</v>
+      </c>
+      <c r="G33">
+        <v>2.38</v>
+      </c>
+      <c r="H33">
+        <v>79.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>20.3</v>
+      </c>
+      <c r="K33">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L33">
+        <v>10.7</v>
+      </c>
+      <c r="M33">
+        <v>4.774279000000001</v>
+      </c>
+      <c r="N33">
+        <v>5.925720999999998</v>
+      </c>
+      <c r="O33">
+        <v>0.5925720999999997</v>
+      </c>
+      <c r="P33">
+        <v>5.333148899999999</v>
+      </c>
+      <c r="Q33">
+        <v>14.9331489</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1743770667903693</v>
+      </c>
+      <c r="T33">
+        <v>1.563188342196157</v>
+      </c>
+      <c r="U33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W33">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.241176102192603</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1461588351399623</v>
+      </c>
+      <c r="C34">
+        <v>113.030428976335</v>
+      </c>
+      <c r="D34">
+        <v>164.570428976335</v>
+      </c>
+      <c r="E34">
+        <v>-34.78</v>
+      </c>
+      <c r="F34">
+        <v>53.92</v>
+      </c>
+      <c r="G34">
+        <v>2.38</v>
+      </c>
+      <c r="H34">
+        <v>79.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>20.3</v>
+      </c>
+      <c r="K34">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L34">
+        <v>10.7</v>
+      </c>
+      <c r="M34">
+        <v>4.928288</v>
+      </c>
+      <c r="N34">
+        <v>5.771711999999999</v>
+      </c>
+      <c r="O34">
+        <v>0.5771711999999998</v>
+      </c>
+      <c r="P34">
+        <v>5.1945408</v>
+      </c>
+      <c r="Q34">
+        <v>14.7945408</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1762288752058269</v>
+      </c>
+      <c r="T34">
+        <v>1.584539485096305</v>
+      </c>
+      <c r="U34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W34">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.171139348999084</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1464968941945698</v>
+      </c>
+      <c r="C35">
+        <v>110.8288446862108</v>
+      </c>
+      <c r="D35">
+        <v>164.0538446862108</v>
+      </c>
+      <c r="E35">
+        <v>-33.095</v>
+      </c>
+      <c r="F35">
+        <v>55.605</v>
+      </c>
+      <c r="G35">
+        <v>2.38</v>
+      </c>
+      <c r="H35">
+        <v>79.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>20.3</v>
+      </c>
+      <c r="K35">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L35">
+        <v>10.7</v>
+      </c>
+      <c r="M35">
+        <v>5.082297000000001</v>
+      </c>
+      <c r="N35">
+        <v>5.617702999999999</v>
+      </c>
+      <c r="O35">
+        <v>0.5617702999999997</v>
+      </c>
+      <c r="P35">
+        <v>5.055932699999999</v>
+      </c>
+      <c r="Q35">
+        <v>14.6559327</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1781359614844325</v>
+      </c>
+      <c r="T35">
+        <v>1.606527975545711</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W35">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.105347247514263</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1468349532491773</v>
+      </c>
+      <c r="C36">
+        <v>108.6304933497093</v>
+      </c>
+      <c r="D36">
+        <v>163.5404933497093</v>
+      </c>
+      <c r="E36">
+        <v>-31.41</v>
+      </c>
+      <c r="F36">
+        <v>57.29000000000001</v>
+      </c>
+      <c r="G36">
+        <v>2.38</v>
+      </c>
+      <c r="H36">
+        <v>79.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>20.3</v>
+      </c>
+      <c r="K36">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L36">
+        <v>10.7</v>
+      </c>
+      <c r="M36">
+        <v>5.236306000000001</v>
+      </c>
+      <c r="N36">
+        <v>5.463693999999998</v>
+      </c>
+      <c r="O36">
+        <v>0.5463693999999998</v>
+      </c>
+      <c r="P36">
+        <v>4.917324599999999</v>
+      </c>
+      <c r="Q36">
+        <v>14.5173246</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1801008382563292</v>
+      </c>
+      <c r="T36">
+        <v>1.629182783887523</v>
+      </c>
+      <c r="U36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W36">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.043425269646197</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1538195123037847</v>
+      </c>
+      <c r="C37">
+        <v>97.01449807124037</v>
+      </c>
+      <c r="D37">
+        <v>153.6094980712404</v>
+      </c>
+      <c r="E37">
+        <v>-29.72499999999999</v>
+      </c>
+      <c r="F37">
+        <v>58.97500000000001</v>
+      </c>
+      <c r="G37">
+        <v>2.38</v>
+      </c>
+      <c r="H37">
+        <v>79.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>20.3</v>
+      </c>
+      <c r="K37">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L37">
+        <v>10.7</v>
+      </c>
+      <c r="M37">
+        <v>6.634687500000001</v>
+      </c>
+      <c r="N37">
+        <v>4.065312499999998</v>
+      </c>
+      <c r="O37">
+        <v>0.4065312499999997</v>
+      </c>
+      <c r="P37">
+        <v>3.658781249999999</v>
+      </c>
+      <c r="Q37">
+        <v>13.25878125</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1821261727750534</v>
+      </c>
+      <c r="T37">
+        <v>1.652534663255237</v>
+      </c>
+      <c r="U37">
+        <v>0.1125</v>
+      </c>
+      <c r="V37">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W37">
+        <v>0.10125</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>1.612736093448259</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1543474713583922</v>
+      </c>
+      <c r="C38">
+        <v>94.62762615291101</v>
+      </c>
+      <c r="D38">
+        <v>152.907626152911</v>
+      </c>
+      <c r="E38">
+        <v>-28.04000000000001</v>
+      </c>
+      <c r="F38">
+        <v>60.66</v>
+      </c>
+      <c r="G38">
+        <v>2.38</v>
+      </c>
+      <c r="H38">
+        <v>79.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>20.3</v>
+      </c>
+      <c r="K38">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L38">
+        <v>10.7</v>
+      </c>
+      <c r="M38">
+        <v>6.82425</v>
+      </c>
+      <c r="N38">
+        <v>3.875749999999999</v>
+      </c>
+      <c r="O38">
+        <v>0.3875749999999998</v>
+      </c>
+      <c r="P38">
+        <v>3.488174999999999</v>
+      </c>
+      <c r="Q38">
+        <v>13.088175</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1842147989974878</v>
+      </c>
+      <c r="T38">
+        <v>1.676616288853193</v>
+      </c>
+      <c r="U38">
+        <v>0.1125</v>
+      </c>
+      <c r="V38">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W38">
+        <v>0.10125</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.567937868630252</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1548754304129997</v>
+      </c>
+      <c r="C39">
+        <v>92.24713904199766</v>
+      </c>
+      <c r="D39">
+        <v>152.2121390419977</v>
+      </c>
+      <c r="E39">
+        <v>-26.355</v>
+      </c>
+      <c r="F39">
+        <v>62.345</v>
+      </c>
+      <c r="G39">
+        <v>2.38</v>
+      </c>
+      <c r="H39">
+        <v>79.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>20.3</v>
+      </c>
+      <c r="K39">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L39">
+        <v>10.7</v>
+      </c>
+      <c r="M39">
+        <v>7.0138125</v>
+      </c>
+      <c r="N39">
+        <v>3.686187499999999</v>
+      </c>
+      <c r="O39">
+        <v>0.3686187499999998</v>
+      </c>
+      <c r="P39">
+        <v>3.317568749999999</v>
+      </c>
+      <c r="Q39">
+        <v>12.91756875</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1863697308142852</v>
+      </c>
+      <c r="T39">
+        <v>1.701462410501876</v>
+      </c>
+      <c r="U39">
+        <v>0.1125</v>
+      </c>
+      <c r="V39">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W39">
+        <v>0.10125</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>1.525561169478083</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1858365400213919</v>
+      </c>
+      <c r="C40">
+        <v>58.51121673437606</v>
+      </c>
+      <c r="D40">
+        <v>120.1612167343761</v>
+      </c>
+      <c r="E40">
+        <v>-24.67</v>
+      </c>
+      <c r="F40">
+        <v>64.03</v>
+      </c>
+      <c r="G40">
+        <v>2.38</v>
+      </c>
+      <c r="H40">
+        <v>79.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>20.3</v>
+      </c>
+      <c r="K40">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L40">
+        <v>10.7</v>
+      </c>
+      <c r="M40">
+        <v>12.588298</v>
+      </c>
+      <c r="N40">
+        <v>-1.888298000000001</v>
+      </c>
+      <c r="O40">
+        <v>-0.1888298</v>
+      </c>
+      <c r="P40">
+        <v>-1.699468200000001</v>
+      </c>
+      <c r="Q40">
+        <v>7.9005318</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1894817554666845</v>
+      </c>
+      <c r="T40">
+        <v>1.737343704974631</v>
+      </c>
+      <c r="U40">
+        <v>0.1966</v>
+      </c>
+      <c r="V40">
+        <v>0.08499957659089416</v>
+      </c>
+      <c r="W40">
+        <v>0.1798890832422302</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.8499957659089417</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1874145400213919</v>
+      </c>
+      <c r="C41">
+        <v>55.55033619146585</v>
+      </c>
+      <c r="D41">
+        <v>118.8853361914659</v>
+      </c>
+      <c r="E41">
+        <v>-22.985</v>
+      </c>
+      <c r="F41">
+        <v>65.715</v>
+      </c>
+      <c r="G41">
+        <v>2.38</v>
+      </c>
+      <c r="H41">
+        <v>79.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>20.3</v>
+      </c>
+      <c r="K41">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L41">
+        <v>10.7</v>
+      </c>
+      <c r="M41">
+        <v>12.919569</v>
+      </c>
+      <c r="N41">
+        <v>-2.219569000000002</v>
+      </c>
+      <c r="O41">
+        <v>-0.2219569000000001</v>
+      </c>
+      <c r="P41">
+        <v>-1.997612100000002</v>
+      </c>
+      <c r="Q41">
+        <v>7.6023879</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1919519481792531</v>
+      </c>
+      <c r="T41">
+        <v>1.765824749318478</v>
+      </c>
+      <c r="U41">
+        <v>0.1966</v>
+      </c>
+      <c r="V41">
+        <v>0.0828201002680507</v>
+      </c>
+      <c r="W41">
+        <v>0.1803175682873012</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8282010026805072</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1889925400213918</v>
+      </c>
+      <c r="C42">
+        <v>52.61626576171341</v>
+      </c>
+      <c r="D42">
+        <v>117.6362657617134</v>
+      </c>
+      <c r="E42">
+        <v>-21.3</v>
+      </c>
+      <c r="F42">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="G42">
+        <v>2.38</v>
+      </c>
+      <c r="H42">
+        <v>79.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>20.3</v>
+      </c>
+      <c r="K42">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L42">
+        <v>10.7</v>
+      </c>
+      <c r="M42">
+        <v>13.25084</v>
+      </c>
+      <c r="N42">
+        <v>-2.550840000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.255084</v>
+      </c>
+      <c r="P42">
+        <v>-2.295756000000001</v>
+      </c>
+      <c r="Q42">
+        <v>7.304244000000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1945044806489073</v>
+      </c>
+      <c r="T42">
+        <v>1.795255161807119</v>
+      </c>
+      <c r="U42">
+        <v>0.1966</v>
+      </c>
+      <c r="V42">
+        <v>0.08074959776134945</v>
+      </c>
+      <c r="W42">
+        <v>0.1807246290801187</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8074959776134947</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1978734007344633</v>
+      </c>
+      <c r="C43">
+        <v>44.3637863074988</v>
+      </c>
+      <c r="D43">
+        <v>111.0687863074988</v>
+      </c>
+      <c r="E43">
+        <v>-19.61499999999999</v>
+      </c>
+      <c r="F43">
+        <v>69.08500000000001</v>
+      </c>
+      <c r="G43">
+        <v>2.38</v>
+      </c>
+      <c r="H43">
+        <v>79.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>20.3</v>
+      </c>
+      <c r="K43">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L43">
+        <v>10.7</v>
+      </c>
+      <c r="M43">
+        <v>14.770373</v>
+      </c>
+      <c r="N43">
+        <v>-4.070373000000002</v>
+      </c>
+      <c r="O43">
+        <v>-0.4070373000000001</v>
+      </c>
+      <c r="P43">
+        <v>-3.663335700000002</v>
+      </c>
+      <c r="Q43">
+        <v>5.9366643</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1975687272922302</v>
+      </c>
+      <c r="T43">
+        <v>1.830585581205131</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.07244231408374045</v>
+      </c>
+      <c r="W43">
+        <v>0.1983118332488963</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.7244231408374047</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1996234007344633</v>
+      </c>
+      <c r="C44">
+        <v>41.47019119540411</v>
+      </c>
+      <c r="D44">
+        <v>109.8601911954041</v>
+      </c>
+      <c r="E44">
+        <v>-17.93000000000001</v>
+      </c>
+      <c r="F44">
+        <v>70.77</v>
+      </c>
+      <c r="G44">
+        <v>2.38</v>
+      </c>
+      <c r="H44">
+        <v>79.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>20.3</v>
+      </c>
+      <c r="K44">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L44">
+        <v>10.7</v>
+      </c>
+      <c r="M44">
+        <v>15.130626</v>
+      </c>
+      <c r="N44">
+        <v>-4.430625999999998</v>
+      </c>
+      <c r="O44">
+        <v>-0.4430625999999998</v>
+      </c>
+      <c r="P44">
+        <v>-3.987563399999999</v>
+      </c>
+      <c r="Q44">
+        <v>5.612436600000002</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2003061191420962</v>
+      </c>
+      <c r="T44">
+        <v>1.862147401570737</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.07071749708174664</v>
+      </c>
+      <c r="W44">
+        <v>0.1986805991239226</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.7071749708174666</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2013734007344633</v>
+      </c>
+      <c r="C45">
+        <v>38.60261560970928</v>
+      </c>
+      <c r="D45">
+        <v>108.6776156097093</v>
+      </c>
+      <c r="E45">
+        <v>-16.245</v>
+      </c>
+      <c r="F45">
+        <v>72.455</v>
+      </c>
+      <c r="G45">
+        <v>2.38</v>
+      </c>
+      <c r="H45">
+        <v>79.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>20.3</v>
+      </c>
+      <c r="K45">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L45">
+        <v>10.7</v>
+      </c>
+      <c r="M45">
+        <v>15.490879</v>
+      </c>
+      <c r="N45">
+        <v>-4.790879</v>
+      </c>
+      <c r="O45">
+        <v>-0.4790878999999999</v>
+      </c>
+      <c r="P45">
+        <v>-4.311791100000001</v>
+      </c>
+      <c r="Q45">
+        <v>5.288208900000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2031395598287996</v>
+      </c>
+      <c r="T45">
+        <v>1.894816654229872</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.06907290412635718</v>
+      </c>
+      <c r="W45">
+        <v>0.1990322130977848</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.6907290412635719</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2031234007344633</v>
+      </c>
+      <c r="C46">
+        <v>35.76022824755067</v>
+      </c>
+      <c r="D46">
+        <v>107.5202282475507</v>
+      </c>
+      <c r="E46">
+        <v>-14.56</v>
+      </c>
+      <c r="F46">
+        <v>74.14</v>
+      </c>
+      <c r="G46">
+        <v>2.38</v>
+      </c>
+      <c r="H46">
+        <v>79.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>20.3</v>
+      </c>
+      <c r="K46">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L46">
+        <v>10.7</v>
+      </c>
+      <c r="M46">
+        <v>15.851132</v>
+      </c>
+      <c r="N46">
+        <v>-5.151132</v>
+      </c>
+      <c r="O46">
+        <v>-0.5151131999999999</v>
+      </c>
+      <c r="P46">
+        <v>-4.6360188</v>
+      </c>
+      <c r="Q46">
+        <v>4.963981200000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2060741948257425</v>
+      </c>
+      <c r="T46">
+        <v>1.928652665912549</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.0675030653962127</v>
+      </c>
+      <c r="W46">
+        <v>0.1993678446182897</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.6750306539621271</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2048734007344633</v>
+      </c>
+      <c r="C47">
+        <v>32.94223284551113</v>
+      </c>
+      <c r="D47">
+        <v>106.3872328455111</v>
+      </c>
+      <c r="E47">
+        <v>-12.875</v>
+      </c>
+      <c r="F47">
+        <v>75.825</v>
+      </c>
+      <c r="G47">
+        <v>2.38</v>
+      </c>
+      <c r="H47">
+        <v>79.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>20.3</v>
+      </c>
+      <c r="K47">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L47">
+        <v>10.7</v>
+      </c>
+      <c r="M47">
+        <v>16.211385</v>
+      </c>
+      <c r="N47">
+        <v>-5.511385000000001</v>
+      </c>
+      <c r="O47">
+        <v>-0.5511385</v>
+      </c>
+      <c r="P47">
+        <v>-4.9602465</v>
+      </c>
+      <c r="Q47">
+        <v>4.639753500000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2091155438225742</v>
+      </c>
+      <c r="T47">
+        <v>1.96371907802005</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.06600299727629685</v>
+      </c>
+      <c r="W47">
+        <v>0.1996885591823277</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6600299727629687</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2066234007344633</v>
+      </c>
+      <c r="C48">
+        <v>30.1478663527285</v>
+      </c>
+      <c r="D48">
+        <v>105.2778663527285</v>
+      </c>
+      <c r="E48">
+        <v>-11.19</v>
+      </c>
+      <c r="F48">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="G48">
+        <v>2.38</v>
+      </c>
+      <c r="H48">
+        <v>79.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>20.3</v>
+      </c>
+      <c r="K48">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L48">
+        <v>10.7</v>
+      </c>
+      <c r="M48">
+        <v>16.571638</v>
+      </c>
+      <c r="N48">
+        <v>-5.871638000000001</v>
+      </c>
+      <c r="O48">
+        <v>-0.5871637999999999</v>
+      </c>
+      <c r="P48">
+        <v>-5.284474200000001</v>
+      </c>
+      <c r="Q48">
+        <v>4.315525800000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2122695353748441</v>
+      </c>
+      <c r="T48">
+        <v>2.000084246131532</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.06456814950942083</v>
+      </c>
+      <c r="W48">
+        <v>0.1999953296348858</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.6456814950942085</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2083734007344633</v>
+      </c>
+      <c r="C49">
+        <v>27.37639721712527</v>
+      </c>
+      <c r="D49">
+        <v>104.1913972171253</v>
+      </c>
+      <c r="E49">
+        <v>-9.504999999999995</v>
+      </c>
+      <c r="F49">
+        <v>79.19500000000001</v>
+      </c>
+      <c r="G49">
+        <v>2.38</v>
+      </c>
+      <c r="H49">
+        <v>79.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>20.3</v>
+      </c>
+      <c r="K49">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L49">
+        <v>10.7</v>
+      </c>
+      <c r="M49">
+        <v>16.931891</v>
+      </c>
+      <c r="N49">
+        <v>-6.231891000000001</v>
+      </c>
+      <c r="O49">
+        <v>-0.6231890999999999</v>
+      </c>
+      <c r="P49">
+        <v>-5.608701900000001</v>
+      </c>
+      <c r="Q49">
+        <v>3.991298100000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2155425454762562</v>
+      </c>
+      <c r="T49">
+        <v>2.037821684737787</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.06319435909432677</v>
+      </c>
+      <c r="W49">
+        <v>0.2002890460256329</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6319435909432679</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2101234007344633</v>
+      </c>
+      <c r="C50">
+        <v>24.62712377667117</v>
+      </c>
+      <c r="D50">
+        <v>103.1271237766712</v>
+      </c>
+      <c r="E50">
+        <v>-7.820000000000007</v>
+      </c>
+      <c r="F50">
+        <v>80.88</v>
+      </c>
+      <c r="G50">
+        <v>2.38</v>
+      </c>
+      <c r="H50">
+        <v>79.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>20.3</v>
+      </c>
+      <c r="K50">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L50">
+        <v>10.7</v>
+      </c>
+      <c r="M50">
+        <v>17.292144</v>
+      </c>
+      <c r="N50">
+        <v>-6.592143999999998</v>
+      </c>
+      <c r="O50">
+        <v>-0.6592143999999996</v>
+      </c>
+      <c r="P50">
+        <v>-5.932929599999998</v>
+      </c>
+      <c r="Q50">
+        <v>3.667070400000004</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2189414405815688</v>
+      </c>
+      <c r="T50">
+        <v>2.077010563290437</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.06187780994652831</v>
+      </c>
+      <c r="W50">
+        <v>0.2005705242334322</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6187780994652833</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2118734007344633</v>
+      </c>
+      <c r="C51">
+        <v>21.8993727482444</v>
+      </c>
+      <c r="D51">
+        <v>102.0843727482444</v>
+      </c>
+      <c r="E51">
+        <v>-6.135000000000005</v>
+      </c>
+      <c r="F51">
+        <v>82.565</v>
+      </c>
+      <c r="G51">
+        <v>2.38</v>
+      </c>
+      <c r="H51">
+        <v>79.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>20.3</v>
+      </c>
+      <c r="K51">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L51">
+        <v>10.7</v>
+      </c>
+      <c r="M51">
+        <v>17.652397</v>
+      </c>
+      <c r="N51">
+        <v>-6.952396999999998</v>
+      </c>
+      <c r="O51">
+        <v>-0.6952396999999996</v>
+      </c>
+      <c r="P51">
+        <v>-6.257157299999998</v>
+      </c>
+      <c r="Q51">
+        <v>3.342842700000003</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2224736256910114</v>
+      </c>
+      <c r="T51">
+        <v>2.117736260609858</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.06061499749863997</v>
+      </c>
+      <c r="W51">
+        <v>0.2008405135347908</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.6061499749863999</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2136234007344633</v>
+      </c>
+      <c r="C52">
+        <v>19.1924978072531</v>
+      </c>
+      <c r="D52">
+        <v>101.0624978072531</v>
+      </c>
+      <c r="E52">
+        <v>-4.450000000000003</v>
+      </c>
+      <c r="F52">
+        <v>84.25</v>
+      </c>
+      <c r="G52">
+        <v>2.38</v>
+      </c>
+      <c r="H52">
+        <v>79.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>20.3</v>
+      </c>
+      <c r="K52">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L52">
+        <v>10.7</v>
+      </c>
+      <c r="M52">
+        <v>18.01265</v>
+      </c>
+      <c r="N52">
+        <v>-7.312650000000001</v>
+      </c>
+      <c r="O52">
+        <v>-0.7312649999999999</v>
+      </c>
+      <c r="P52">
+        <v>-6.581385000000002</v>
+      </c>
+      <c r="Q52">
+        <v>3.018615</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2261470982048316</v>
+      </c>
+      <c r="T52">
+        <v>2.160090985822055</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.05940269754866717</v>
+      </c>
+      <c r="W52">
+        <v>0.2010997032640949</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5940269754866718</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2153734007344633</v>
+      </c>
+      <c r="C53">
+        <v>16.50587825171958</v>
+      </c>
+      <c r="D53">
+        <v>100.0608782517196</v>
+      </c>
+      <c r="E53">
+        <v>-2.765000000000001</v>
+      </c>
+      <c r="F53">
+        <v>85.935</v>
+      </c>
+      <c r="G53">
+        <v>2.38</v>
+      </c>
+      <c r="H53">
+        <v>79.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>20.3</v>
+      </c>
+      <c r="K53">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L53">
+        <v>10.7</v>
+      </c>
+      <c r="M53">
+        <v>18.372903</v>
+      </c>
+      <c r="N53">
+        <v>-7.672903000000002</v>
+      </c>
+      <c r="O53">
+        <v>-0.7672903</v>
+      </c>
+      <c r="P53">
+        <v>-6.905612700000002</v>
+      </c>
+      <c r="Q53">
+        <v>2.6943873</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2299705083722772</v>
+      </c>
+      <c r="T53">
+        <v>2.204174475328628</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.0582379387732031</v>
+      </c>
+      <c r="W53">
+        <v>0.2013487286902892</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5823793877320311</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2171234007344633</v>
+      </c>
+      <c r="C54">
+        <v>13.83891774502618</v>
+      </c>
+      <c r="D54">
+        <v>99.07891774502619</v>
+      </c>
+      <c r="E54">
+        <v>-1.079999999999998</v>
+      </c>
+      <c r="F54">
+        <v>87.62</v>
+      </c>
+      <c r="G54">
+        <v>2.38</v>
+      </c>
+      <c r="H54">
+        <v>79.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>20.3</v>
+      </c>
+      <c r="K54">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L54">
+        <v>10.7</v>
+      </c>
+      <c r="M54">
+        <v>18.733156</v>
+      </c>
+      <c r="N54">
+        <v>-8.033156000000002</v>
+      </c>
+      <c r="O54">
+        <v>-0.8033156</v>
+      </c>
+      <c r="P54">
+        <v>-7.229840400000001</v>
+      </c>
+      <c r="Q54">
+        <v>2.3701596</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2339532272966996</v>
+      </c>
+      <c r="T54">
+        <v>2.250094776897974</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.05711797841217997</v>
+      </c>
+      <c r="W54">
+        <v>0.2015881762154759</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5711797841217998</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2188734007344633</v>
+      </c>
+      <c r="C55">
+        <v>11.1910431319706</v>
+      </c>
+      <c r="D55">
+        <v>98.11604313197061</v>
+      </c>
+      <c r="E55">
+        <v>0.605000000000004</v>
+      </c>
+      <c r="F55">
+        <v>89.30500000000001</v>
+      </c>
+      <c r="G55">
+        <v>2.38</v>
+      </c>
+      <c r="H55">
+        <v>79.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>20.3</v>
+      </c>
+      <c r="K55">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L55">
+        <v>10.7</v>
+      </c>
+      <c r="M55">
+        <v>19.093409</v>
+      </c>
+      <c r="N55">
+        <v>-8.393409000000002</v>
+      </c>
+      <c r="O55">
+        <v>-0.8393409000000001</v>
+      </c>
+      <c r="P55">
+        <v>-7.554068100000002</v>
+      </c>
+      <c r="Q55">
+        <v>2.045931899999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2381054236221613</v>
+      </c>
+      <c r="T55">
+        <v>2.29796913385325</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.05604028070628978</v>
+      </c>
+      <c r="W55">
+        <v>0.2018185879849952</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5604028070628979</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2206234007344633</v>
+      </c>
+      <c r="C56">
+        <v>8.561703323192603</v>
+      </c>
+      <c r="D56">
+        <v>97.17170332319262</v>
+      </c>
+      <c r="E56">
+        <v>2.290000000000006</v>
+      </c>
+      <c r="F56">
+        <v>90.99000000000001</v>
+      </c>
+      <c r="G56">
+        <v>2.38</v>
+      </c>
+      <c r="H56">
+        <v>79.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>20.3</v>
+      </c>
+      <c r="K56">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L56">
+        <v>10.7</v>
+      </c>
+      <c r="M56">
+        <v>19.453662</v>
+      </c>
+      <c r="N56">
+        <v>-8.753662000000002</v>
+      </c>
+      <c r="O56">
+        <v>-0.8753662</v>
+      </c>
+      <c r="P56">
+        <v>-7.878295800000002</v>
+      </c>
+      <c r="Q56">
+        <v>1.7217042</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2424381502226431</v>
+      </c>
+      <c r="T56">
+        <v>2.347924984589191</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.05500249773024738</v>
+      </c>
+      <c r="W56">
+        <v>0.2020404659852731</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5500249773024739</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2223734007344633</v>
+      </c>
+      <c r="C57">
+        <v>5.950368243408562</v>
+      </c>
+      <c r="D57">
+        <v>96.24536824340858</v>
+      </c>
+      <c r="E57">
+        <v>3.975000000000009</v>
+      </c>
+      <c r="F57">
+        <v>92.67500000000001</v>
+      </c>
+      <c r="G57">
+        <v>2.38</v>
+      </c>
+      <c r="H57">
+        <v>79.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>20.3</v>
+      </c>
+      <c r="K57">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L57">
+        <v>10.7</v>
+      </c>
+      <c r="M57">
+        <v>19.813915</v>
+      </c>
+      <c r="N57">
+        <v>-9.113915000000002</v>
+      </c>
+      <c r="O57">
+        <v>-0.9113915</v>
+      </c>
+      <c r="P57">
+        <v>-8.202523500000002</v>
+      </c>
+      <c r="Q57">
+        <v>1.3974765</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2469634424498129</v>
+      </c>
+      <c r="T57">
+        <v>2.400101095357839</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.05400245231697015</v>
+      </c>
+      <c r="W57">
+        <v>0.2022542756946318</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5400245231697016</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2241234007344633</v>
+      </c>
+      <c r="C58">
+        <v>3.356527839236946</v>
+      </c>
+      <c r="D58">
+        <v>95.33652783923696</v>
+      </c>
+      <c r="E58">
+        <v>5.660000000000011</v>
+      </c>
+      <c r="F58">
+        <v>94.36000000000001</v>
+      </c>
+      <c r="G58">
+        <v>2.38</v>
+      </c>
+      <c r="H58">
+        <v>79.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>20.3</v>
+      </c>
+      <c r="K58">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L58">
+        <v>10.7</v>
+      </c>
+      <c r="M58">
+        <v>20.174168</v>
+      </c>
+      <c r="N58">
+        <v>-9.474168000000002</v>
+      </c>
+      <c r="O58">
+        <v>-0.9474168000000001</v>
+      </c>
+      <c r="P58">
+        <v>-8.526751200000003</v>
+      </c>
+      <c r="Q58">
+        <v>1.073248799999998</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2516944297782178</v>
+      </c>
+      <c r="T58">
+        <v>2.454648847525062</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.05303812281130997</v>
+      </c>
+      <c r="W58">
+        <v>0.2024604493429419</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5303812281130997</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2258734007344633</v>
+      </c>
+      <c r="C59">
+        <v>0.7796911427122524</v>
+      </c>
+      <c r="D59">
+        <v>94.44469114271227</v>
+      </c>
+      <c r="E59">
+        <v>7.345000000000013</v>
+      </c>
+      <c r="F59">
+        <v>96.04500000000002</v>
+      </c>
+      <c r="G59">
+        <v>2.38</v>
+      </c>
+      <c r="H59">
+        <v>79.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>20.3</v>
+      </c>
+      <c r="K59">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L59">
+        <v>10.7</v>
+      </c>
+      <c r="M59">
+        <v>20.534421</v>
+      </c>
+      <c r="N59">
+        <v>-9.834421000000003</v>
+      </c>
+      <c r="O59">
+        <v>-0.9834421</v>
+      </c>
+      <c r="P59">
+        <v>-8.850978900000003</v>
+      </c>
+      <c r="Q59">
+        <v>0.7490210999999984</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.256645463028874</v>
+      </c>
+      <c r="T59">
+        <v>2.51173370444425</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.05210762942865541</v>
+      </c>
+      <c r="W59">
+        <v>0.2026593888281535</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5210762942865541</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2276234007344633</v>
+      </c>
+      <c r="C60">
+        <v>-1.780614613125536</v>
+      </c>
+      <c r="D60">
+        <v>93.56938538687446</v>
+      </c>
+      <c r="E60">
+        <v>9.029999999999987</v>
+      </c>
+      <c r="F60">
+        <v>97.72999999999999</v>
+      </c>
+      <c r="G60">
+        <v>2.38</v>
+      </c>
+      <c r="H60">
+        <v>79.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>20.3</v>
+      </c>
+      <c r="K60">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L60">
+        <v>10.7</v>
+      </c>
+      <c r="M60">
+        <v>20.894674</v>
+      </c>
+      <c r="N60">
+        <v>-10.194674</v>
+      </c>
+      <c r="O60">
+        <v>-1.0194674</v>
+      </c>
+      <c r="P60">
+        <v>-9.175206599999999</v>
+      </c>
+      <c r="Q60">
+        <v>0.4247934000000022</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2618322597676567</v>
+      </c>
+      <c r="T60">
+        <v>2.571536887883398</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.05120922202471308</v>
+      </c>
+      <c r="W60">
+        <v>0.2028514683311163</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.512092220247131</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2293734007344633</v>
+      </c>
+      <c r="C61">
+        <v>-4.324844829913175</v>
+      </c>
+      <c r="D61">
+        <v>92.71015517008682</v>
+      </c>
+      <c r="E61">
+        <v>10.71499999999999</v>
+      </c>
+      <c r="F61">
+        <v>99.41499999999999</v>
+      </c>
+      <c r="G61">
+        <v>2.38</v>
+      </c>
+      <c r="H61">
+        <v>79.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>20.3</v>
+      </c>
+      <c r="K61">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L61">
+        <v>10.7</v>
+      </c>
+      <c r="M61">
+        <v>21.254927</v>
+      </c>
+      <c r="N61">
+        <v>-10.554927</v>
+      </c>
+      <c r="O61">
+        <v>-1.0554927</v>
+      </c>
+      <c r="P61">
+        <v>-9.499434299999999</v>
+      </c>
+      <c r="Q61">
+        <v>0.1005657000000024</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.267272070981502</v>
+      </c>
+      <c r="T61">
+        <v>2.634257299782993</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.05034126910903998</v>
+      </c>
+      <c r="W61">
+        <v>0.2030370366644872</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5034126910903999</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2464235887882852</v>
+      </c>
+      <c r="C62">
+        <v>-13.62326481448376</v>
+      </c>
+      <c r="D62">
+        <v>85.09673518551624</v>
+      </c>
+      <c r="E62">
+        <v>12.39999999999999</v>
+      </c>
+      <c r="F62">
+        <v>101.1</v>
+      </c>
+      <c r="G62">
+        <v>2.38</v>
+      </c>
+      <c r="H62">
+        <v>79.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>20.3</v>
+      </c>
+      <c r="K62">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L62">
+        <v>10.7</v>
+      </c>
+      <c r="M62">
+        <v>24.14268</v>
+      </c>
+      <c r="N62">
+        <v>-13.44268</v>
+      </c>
+      <c r="O62">
+        <v>-1.344268</v>
+      </c>
+      <c r="P62">
+        <v>-12.098412</v>
+      </c>
+      <c r="Q62">
+        <v>-2.498411999999998</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2737343428905944</v>
+      </c>
+      <c r="T62">
+        <v>2.708766568581487</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04431985181429732</v>
+      </c>
+      <c r="W62">
+        <v>0.2282164193867458</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.4431985181429734</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2484235887882852</v>
+      </c>
+      <c r="C63">
+        <v>-16.12016518960291</v>
+      </c>
+      <c r="D63">
+        <v>84.28483481039709</v>
+      </c>
+      <c r="E63">
+        <v>14.08499999999999</v>
+      </c>
+      <c r="F63">
+        <v>102.785</v>
+      </c>
+      <c r="G63">
+        <v>2.38</v>
+      </c>
+      <c r="H63">
+        <v>79.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>20.3</v>
+      </c>
+      <c r="K63">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L63">
+        <v>10.7</v>
+      </c>
+      <c r="M63">
+        <v>24.545058</v>
+      </c>
+      <c r="N63">
+        <v>-13.845058</v>
+      </c>
+      <c r="O63">
+        <v>-1.3845058</v>
+      </c>
+      <c r="P63">
+        <v>-12.4605522</v>
+      </c>
+      <c r="Q63">
+        <v>-2.860552200000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2797583004006096</v>
+      </c>
+      <c r="T63">
+        <v>2.778222121622038</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04359329686652196</v>
+      </c>
+      <c r="W63">
+        <v>0.2283899207082746</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4359329686652197</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2504235887882852</v>
+      </c>
+      <c r="C64">
+        <v>-18.6017194423022</v>
+      </c>
+      <c r="D64">
+        <v>83.48828055769781</v>
+      </c>
+      <c r="E64">
+        <v>15.77</v>
+      </c>
+      <c r="F64">
+        <v>104.47</v>
+      </c>
+      <c r="G64">
+        <v>2.38</v>
+      </c>
+      <c r="H64">
+        <v>79.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>20.3</v>
+      </c>
+      <c r="K64">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L64">
+        <v>10.7</v>
+      </c>
+      <c r="M64">
+        <v>24.947436</v>
+      </c>
+      <c r="N64">
+        <v>-14.247436</v>
+      </c>
+      <c r="O64">
+        <v>-1.4247436</v>
+      </c>
+      <c r="P64">
+        <v>-12.8226924</v>
+      </c>
+      <c r="Q64">
+        <v>-3.2226924</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2860993083058888</v>
+      </c>
+      <c r="T64">
+        <v>2.851333230085776</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.04289017917512644</v>
+      </c>
+      <c r="W64">
+        <v>0.2285578252129798</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4289017917512645</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2524235887882852</v>
+      </c>
+      <c r="C65">
+        <v>-21.06835859583633</v>
+      </c>
+      <c r="D65">
+        <v>82.70664140416368</v>
+      </c>
+      <c r="E65">
+        <v>17.455</v>
+      </c>
+      <c r="F65">
+        <v>106.155</v>
+      </c>
+      <c r="G65">
+        <v>2.38</v>
+      </c>
+      <c r="H65">
+        <v>79.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>20.3</v>
+      </c>
+      <c r="K65">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L65">
+        <v>10.7</v>
+      </c>
+      <c r="M65">
+        <v>25.349814</v>
+      </c>
+      <c r="N65">
+        <v>-14.649814</v>
+      </c>
+      <c r="O65">
+        <v>-1.4649814</v>
+      </c>
+      <c r="P65">
+        <v>-13.1848326</v>
+      </c>
+      <c r="Q65">
+        <v>-3.584832600000002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2927830733952372</v>
+      </c>
+      <c r="T65">
+        <v>2.928396290358365</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.04220938268028316</v>
+      </c>
+      <c r="W65">
+        <v>0.2287203994159484</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4220938268028317</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2544235887882852</v>
+      </c>
+      <c r="C66">
+        <v>-23.52049768176789</v>
+      </c>
+      <c r="D66">
+        <v>81.93950231823212</v>
+      </c>
+      <c r="E66">
+        <v>19.14</v>
+      </c>
+      <c r="F66">
+        <v>107.84</v>
+      </c>
+      <c r="G66">
+        <v>2.38</v>
+      </c>
+      <c r="H66">
+        <v>79.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>20.3</v>
+      </c>
+      <c r="K66">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L66">
+        <v>10.7</v>
+      </c>
+      <c r="M66">
+        <v>25.752192</v>
+      </c>
+      <c r="N66">
+        <v>-15.052192</v>
+      </c>
+      <c r="O66">
+        <v>-1.5052192</v>
+      </c>
+      <c r="P66">
+        <v>-13.5469728</v>
+      </c>
+      <c r="Q66">
+        <v>-3.946972800000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2998381587673271</v>
+      </c>
+      <c r="T66">
+        <v>3.009740631757208</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.04154986107590374</v>
+      </c>
+      <c r="W66">
+        <v>0.2288778931750742</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4154986107590375</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2564235887882853</v>
+      </c>
+      <c r="C67">
+        <v>-25.95853647480007</v>
+      </c>
+      <c r="D67">
+        <v>81.18646352519994</v>
+      </c>
+      <c r="E67">
+        <v>20.825</v>
+      </c>
+      <c r="F67">
+        <v>109.525</v>
+      </c>
+      <c r="G67">
+        <v>2.38</v>
+      </c>
+      <c r="H67">
+        <v>79.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>20.3</v>
+      </c>
+      <c r="K67">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L67">
+        <v>10.7</v>
+      </c>
+      <c r="M67">
+        <v>26.15457</v>
+      </c>
+      <c r="N67">
+        <v>-15.45457</v>
+      </c>
+      <c r="O67">
+        <v>-1.545457</v>
+      </c>
+      <c r="P67">
+        <v>-13.909113</v>
+      </c>
+      <c r="Q67">
+        <v>-4.309113000000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.307296391874965</v>
+      </c>
+      <c r="T67">
+        <v>3.095733221235986</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.04091063244396675</v>
+      </c>
+      <c r="W67">
+        <v>0.2290305409723808</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.4091063244396677</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2584235887882852</v>
+      </c>
+      <c r="C68">
+        <v>-28.38286018745883</v>
+      </c>
+      <c r="D68">
+        <v>80.44713981254118</v>
+      </c>
+      <c r="E68">
+        <v>22.51000000000001</v>
+      </c>
+      <c r="F68">
+        <v>111.21</v>
+      </c>
+      <c r="G68">
+        <v>2.38</v>
+      </c>
+      <c r="H68">
+        <v>79.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>20.3</v>
+      </c>
+      <c r="K68">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L68">
+        <v>10.7</v>
+      </c>
+      <c r="M68">
+        <v>26.556948</v>
+      </c>
+      <c r="N68">
+        <v>-15.856948</v>
+      </c>
+      <c r="O68">
+        <v>-1.5856948</v>
+      </c>
+      <c r="P68">
+        <v>-14.2712532</v>
+      </c>
+      <c r="Q68">
+        <v>-4.671253200000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3151933445771699</v>
+      </c>
+      <c r="T68">
+        <v>3.186784198331162</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.04029077437663393</v>
+      </c>
+      <c r="W68">
+        <v>0.2291785630788598</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.4029077437663393</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2604235887882853</v>
+      </c>
+      <c r="C69">
+        <v>-30.79384012716096</v>
+      </c>
+      <c r="D69">
+        <v>79.72115987283905</v>
+      </c>
+      <c r="E69">
+        <v>24.19500000000001</v>
+      </c>
+      <c r="F69">
+        <v>112.895</v>
+      </c>
+      <c r="G69">
+        <v>2.38</v>
+      </c>
+      <c r="H69">
+        <v>79.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>20.3</v>
+      </c>
+      <c r="K69">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L69">
+        <v>10.7</v>
+      </c>
+      <c r="M69">
+        <v>26.959326</v>
+      </c>
+      <c r="N69">
+        <v>-16.25932600000001</v>
+      </c>
+      <c r="O69">
+        <v>-1.6259326</v>
+      </c>
+      <c r="P69">
+        <v>-14.6333934</v>
+      </c>
+      <c r="Q69">
+        <v>-5.033393400000003</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3235689004734478</v>
+      </c>
+      <c r="T69">
+        <v>3.283353416462409</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03968941953519162</v>
+      </c>
+      <c r="W69">
+        <v>0.2293221666149962</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3968941953519164</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2624235887882853</v>
+      </c>
+      <c r="C70">
+        <v>-33.1918343180226</v>
+      </c>
+      <c r="D70">
+        <v>79.00816568197742</v>
+      </c>
+      <c r="E70">
+        <v>25.88000000000001</v>
+      </c>
+      <c r="F70">
+        <v>114.58</v>
+      </c>
+      <c r="G70">
+        <v>2.38</v>
+      </c>
+      <c r="H70">
+        <v>79.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>20.3</v>
+      </c>
+      <c r="K70">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L70">
+        <v>10.7</v>
+      </c>
+      <c r="M70">
+        <v>27.361704</v>
+      </c>
+      <c r="N70">
+        <v>-16.661704</v>
+      </c>
+      <c r="O70">
+        <v>-1.6661704</v>
+      </c>
+      <c r="P70">
+        <v>-14.9955336</v>
+      </c>
+      <c r="Q70">
+        <v>-5.395533600000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.332467928613243</v>
+      </c>
+      <c r="T70">
+        <v>3.38595821072686</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03910575160085058</v>
+      </c>
+      <c r="W70">
+        <v>0.2294615465177169</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3910575160085058</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2644235887882852</v>
+      </c>
+      <c r="C71">
+        <v>-35.57718808959667</v>
+      </c>
+      <c r="D71">
+        <v>78.30781191040334</v>
+      </c>
+      <c r="E71">
+        <v>27.56500000000001</v>
+      </c>
+      <c r="F71">
+        <v>116.265</v>
+      </c>
+      <c r="G71">
+        <v>2.38</v>
+      </c>
+      <c r="H71">
+        <v>79.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>20.3</v>
+      </c>
+      <c r="K71">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L71">
+        <v>10.7</v>
+      </c>
+      <c r="M71">
+        <v>27.76408200000001</v>
+      </c>
+      <c r="N71">
+        <v>-17.06408200000001</v>
+      </c>
+      <c r="O71">
+        <v>-1.7064082</v>
+      </c>
+      <c r="P71">
+        <v>-15.35767380000001</v>
+      </c>
+      <c r="Q71">
+        <v>-5.757673800000005</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.341941087600767</v>
+      </c>
+      <c r="T71">
+        <v>3.495182669137403</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03853900157764983</v>
+      </c>
+      <c r="W71">
+        <v>0.2295968864232572</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3853900157764985</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2664235887882853</v>
+      </c>
+      <c r="C72">
+        <v>-37.95023463457265</v>
+      </c>
+      <c r="D72">
+        <v>77.61976536542737</v>
+      </c>
+      <c r="E72">
+        <v>29.25000000000001</v>
+      </c>
+      <c r="F72">
+        <v>117.95</v>
+      </c>
+      <c r="G72">
+        <v>2.38</v>
+      </c>
+      <c r="H72">
+        <v>79.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>20.3</v>
+      </c>
+      <c r="K72">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L72">
+        <v>10.7</v>
+      </c>
+      <c r="M72">
+        <v>28.16646</v>
+      </c>
+      <c r="N72">
+        <v>-17.46646</v>
+      </c>
+      <c r="O72">
+        <v>-1.746646</v>
+      </c>
+      <c r="P72">
+        <v>-15.719814</v>
+      </c>
+      <c r="Q72">
+        <v>-6.119814000000003</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3520457905207926</v>
+      </c>
+      <c r="T72">
+        <v>3.611688758108651</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03798844441225484</v>
+      </c>
+      <c r="W72">
+        <v>0.2297283594743536</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3798844441225485</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2684235887882852</v>
+      </c>
+      <c r="C73">
+        <v>-40.31129553733109</v>
+      </c>
+      <c r="D73">
+        <v>76.9437044626689</v>
+      </c>
+      <c r="E73">
+        <v>30.93499999999999</v>
+      </c>
+      <c r="F73">
+        <v>119.635</v>
+      </c>
+      <c r="G73">
+        <v>2.38</v>
+      </c>
+      <c r="H73">
+        <v>79.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>20.3</v>
+      </c>
+      <c r="K73">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L73">
+        <v>10.7</v>
+      </c>
+      <c r="M73">
+        <v>28.568838</v>
+      </c>
+      <c r="N73">
+        <v>-17.868838</v>
+      </c>
+      <c r="O73">
+        <v>-1.7868838</v>
+      </c>
+      <c r="P73">
+        <v>-16.0819542</v>
+      </c>
+      <c r="Q73">
+        <v>-6.481954200000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3628473695042681</v>
+      </c>
+      <c r="T73">
+        <v>3.736229749767568</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03745339589940619</v>
+      </c>
+      <c r="W73">
+        <v>0.2298561290592218</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3745339589940619</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2704235887882852</v>
+      </c>
+      <c r="C74">
+        <v>-42.66068127511534</v>
+      </c>
+      <c r="D74">
+        <v>76.27931872488466</v>
+      </c>
+      <c r="E74">
+        <v>32.61999999999999</v>
+      </c>
+      <c r="F74">
+        <v>121.32</v>
+      </c>
+      <c r="G74">
+        <v>2.38</v>
+      </c>
+      <c r="H74">
+        <v>79.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>20.3</v>
+      </c>
+      <c r="K74">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L74">
+        <v>10.7</v>
+      </c>
+      <c r="M74">
+        <v>28.971216</v>
+      </c>
+      <c r="N74">
+        <v>-18.271216</v>
+      </c>
+      <c r="O74">
+        <v>-1.827121599999999</v>
+      </c>
+      <c r="P74">
+        <v>-16.4440944</v>
+      </c>
+      <c r="Q74">
+        <v>-6.844094399999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3744204898437062</v>
+      </c>
+      <c r="T74">
+        <v>3.869666526544982</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03693320984524777</v>
+      </c>
+      <c r="W74">
+        <v>0.2299803494889548</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3693320984524778</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2724235887882853</v>
+      </c>
+      <c r="C75">
+        <v>-44.9986916934598</v>
+      </c>
+      <c r="D75">
+        <v>75.6263083065402</v>
+      </c>
+      <c r="E75">
+        <v>34.30499999999999</v>
+      </c>
+      <c r="F75">
+        <v>123.005</v>
+      </c>
+      <c r="G75">
+        <v>2.38</v>
+      </c>
+      <c r="H75">
+        <v>79.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>20.3</v>
+      </c>
+      <c r="K75">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L75">
+        <v>10.7</v>
+      </c>
+      <c r="M75">
+        <v>29.373594</v>
+      </c>
+      <c r="N75">
+        <v>-18.673594</v>
+      </c>
+      <c r="O75">
+        <v>-1.8673594</v>
+      </c>
+      <c r="P75">
+        <v>-16.8062346</v>
+      </c>
+      <c r="Q75">
+        <v>-7.206234600000002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3868508783564361</v>
+      </c>
+      <c r="T75">
+        <v>4.01298750900961</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03642727546380602</v>
+      </c>
+      <c r="W75">
+        <v>0.2301011666192432</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3642727546380603</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2744235887882852</v>
+      </c>
+      <c r="C76">
+        <v>-47.325616457406</v>
+      </c>
+      <c r="D76">
+        <v>74.984383542594</v>
+      </c>
+      <c r="E76">
+        <v>35.98999999999999</v>
+      </c>
+      <c r="F76">
+        <v>124.69</v>
+      </c>
+      <c r="G76">
+        <v>2.38</v>
+      </c>
+      <c r="H76">
+        <v>79.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>20.3</v>
+      </c>
+      <c r="K76">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L76">
+        <v>10.7</v>
+      </c>
+      <c r="M76">
+        <v>29.775972</v>
+      </c>
+      <c r="N76">
+        <v>-19.075972</v>
+      </c>
+      <c r="O76">
+        <v>-1.9075972</v>
+      </c>
+      <c r="P76">
+        <v>-17.1683748</v>
+      </c>
+      <c r="Q76">
+        <v>-7.568374800000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4002374506009144</v>
+      </c>
+      <c r="T76">
+        <v>4.167333182433057</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0359350149845654</v>
+      </c>
+      <c r="W76">
+        <v>0.2302187184216858</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3593501498456541</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2764235887882852</v>
+      </c>
+      <c r="C77">
+        <v>-49.64173547993202</v>
+      </c>
+      <c r="D77">
+        <v>74.35326452006798</v>
+      </c>
+      <c r="E77">
+        <v>37.675</v>
+      </c>
+      <c r="F77">
+        <v>126.375</v>
+      </c>
+      <c r="G77">
+        <v>2.38</v>
+      </c>
+      <c r="H77">
+        <v>79.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>20.3</v>
+      </c>
+      <c r="K77">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L77">
+        <v>10.7</v>
+      </c>
+      <c r="M77">
+        <v>30.17835</v>
+      </c>
+      <c r="N77">
+        <v>-19.47835</v>
+      </c>
+      <c r="O77">
+        <v>-1.947835</v>
+      </c>
+      <c r="P77">
+        <v>-17.530515</v>
+      </c>
+      <c r="Q77">
+        <v>-7.930515</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.414694948624951</v>
+      </c>
+      <c r="T77">
+        <v>4.334026509730379</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03545588145143785</v>
+      </c>
+      <c r="W77">
+        <v>0.2303331355093967</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3545588145143787</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2784235887882853</v>
+      </c>
+      <c r="C78">
+        <v>-51.94731932892667</v>
+      </c>
+      <c r="D78">
+        <v>73.73268067107334</v>
+      </c>
+      <c r="E78">
+        <v>39.36</v>
+      </c>
+      <c r="F78">
+        <v>128.06</v>
+      </c>
+      <c r="G78">
+        <v>2.38</v>
+      </c>
+      <c r="H78">
+        <v>79.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>20.3</v>
+      </c>
+      <c r="K78">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L78">
+        <v>10.7</v>
+      </c>
+      <c r="M78">
+        <v>30.580728</v>
+      </c>
+      <c r="N78">
+        <v>-19.880728</v>
+      </c>
+      <c r="O78">
+        <v>-1.9880728</v>
+      </c>
+      <c r="P78">
+        <v>-17.8926552</v>
+      </c>
+      <c r="Q78">
+        <v>-8.292655199999999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4303572381509907</v>
+      </c>
+      <c r="T78">
+        <v>4.514610947635813</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03498935669549788</v>
+      </c>
+      <c r="W78">
+        <v>0.2304445416211151</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.349893566954979</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2804235887882852</v>
+      </c>
+      <c r="C79">
+        <v>-54.24262961395166</v>
+      </c>
+      <c r="D79">
+        <v>73.12237038604835</v>
+      </c>
+      <c r="E79">
+        <v>41.045</v>
+      </c>
+      <c r="F79">
+        <v>129.745</v>
+      </c>
+      <c r="G79">
+        <v>2.38</v>
+      </c>
+      <c r="H79">
+        <v>79.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>20.3</v>
+      </c>
+      <c r="K79">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L79">
+        <v>10.7</v>
+      </c>
+      <c r="M79">
+        <v>30.983106</v>
+      </c>
+      <c r="N79">
+        <v>-20.283106</v>
+      </c>
+      <c r="O79">
+        <v>-2.0283106</v>
+      </c>
+      <c r="P79">
+        <v>-18.2547954</v>
+      </c>
+      <c r="Q79">
+        <v>-8.654795400000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.447381465896686</v>
+      </c>
+      <c r="T79">
+        <v>4.710898380141718</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03453494946568622</v>
+      </c>
+      <c r="W79">
+        <v>0.2305530540675941</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3453494946568623</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2824235887882852</v>
+      </c>
+      <c r="C80">
+        <v>-56.52791935395376</v>
+      </c>
+      <c r="D80">
+        <v>72.52208064604625</v>
+      </c>
+      <c r="E80">
+        <v>42.73</v>
+      </c>
+      <c r="F80">
+        <v>131.43</v>
+      </c>
+      <c r="G80">
+        <v>2.38</v>
+      </c>
+      <c r="H80">
+        <v>79.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>20.3</v>
+      </c>
+      <c r="K80">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L80">
+        <v>10.7</v>
+      </c>
+      <c r="M80">
+        <v>31.385484</v>
+      </c>
+      <c r="N80">
+        <v>-20.685484</v>
+      </c>
+      <c r="O80">
+        <v>-2.0685484</v>
+      </c>
+      <c r="P80">
+        <v>-18.6169356</v>
+      </c>
+      <c r="Q80">
+        <v>-9.0169356</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4659533507101717</v>
+      </c>
+      <c r="T80">
+        <v>4.925030124693614</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03409219370330564</v>
+      </c>
+      <c r="W80">
+        <v>0.2306587841436506</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3409219370330564</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2844235887882853</v>
+      </c>
+      <c r="C81">
+        <v>-58.80343332701162</v>
+      </c>
+      <c r="D81">
+        <v>71.9315666729884</v>
+      </c>
+      <c r="E81">
+        <v>44.41500000000001</v>
+      </c>
+      <c r="F81">
+        <v>133.115</v>
+      </c>
+      <c r="G81">
+        <v>2.38</v>
+      </c>
+      <c r="H81">
+        <v>79.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>20.3</v>
+      </c>
+      <c r="K81">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L81">
+        <v>10.7</v>
+      </c>
+      <c r="M81">
+        <v>31.787862</v>
+      </c>
+      <c r="N81">
+        <v>-21.087862</v>
+      </c>
+      <c r="O81">
+        <v>-2.1087862</v>
+      </c>
+      <c r="P81">
+        <v>-18.9790758</v>
+      </c>
+      <c r="Q81">
+        <v>-9.379075800000003</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4862939864582752</v>
+      </c>
+      <c r="T81">
+        <v>5.159555368726644</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03366064694756758</v>
+      </c>
+      <c r="W81">
+        <v>0.2307618375089209</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3366064694756759</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2864235887882852</v>
+      </c>
+      <c r="C82">
+        <v>-61.06940840313399</v>
+      </c>
+      <c r="D82">
+        <v>71.35059159686602</v>
+      </c>
+      <c r="E82">
+        <v>46.10000000000001</v>
+      </c>
+      <c r="F82">
+        <v>134.8</v>
+      </c>
+      <c r="G82">
+        <v>2.38</v>
+      </c>
+      <c r="H82">
+        <v>79.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>20.3</v>
+      </c>
+      <c r="K82">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L82">
+        <v>10.7</v>
+      </c>
+      <c r="M82">
+        <v>32.19024</v>
+      </c>
+      <c r="N82">
+        <v>-21.49024</v>
+      </c>
+      <c r="O82">
+        <v>-2.149024</v>
+      </c>
+      <c r="P82">
+        <v>-19.341216</v>
+      </c>
+      <c r="Q82">
+        <v>-9.741216000000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5086686857811888</v>
+      </c>
+      <c r="T82">
+        <v>5.417533137162976</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.033239888860723</v>
+      </c>
+      <c r="W82">
+        <v>0.2308623145400593</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.33239888860723</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2884235887882852</v>
+      </c>
+      <c r="C83">
+        <v>-63.3260738610598</v>
+      </c>
+      <c r="D83">
+        <v>70.77892613894022</v>
+      </c>
+      <c r="E83">
+        <v>47.78500000000001</v>
+      </c>
+      <c r="F83">
+        <v>136.485</v>
+      </c>
+      <c r="G83">
+        <v>2.38</v>
+      </c>
+      <c r="H83">
+        <v>79.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>20.3</v>
+      </c>
+      <c r="K83">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L83">
+        <v>10.7</v>
+      </c>
+      <c r="M83">
+        <v>32.592618</v>
+      </c>
+      <c r="N83">
+        <v>-21.892618</v>
+      </c>
+      <c r="O83">
+        <v>-2.1892618</v>
+      </c>
+      <c r="P83">
+        <v>-19.7033562</v>
+      </c>
+      <c r="Q83">
+        <v>-10.1033562</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5333986166117777</v>
+      </c>
+      <c r="T83">
+        <v>5.702666460171553</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03282951986244246</v>
+      </c>
+      <c r="W83">
+        <v>0.2309603106568488</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3282951986244247</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2904235887882852</v>
+      </c>
+      <c r="C84">
+        <v>-65.57365168994923</v>
+      </c>
+      <c r="D84">
+        <v>70.21634831005079</v>
+      </c>
+      <c r="E84">
+        <v>49.47000000000001</v>
+      </c>
+      <c r="F84">
+        <v>138.17</v>
+      </c>
+      <c r="G84">
+        <v>2.38</v>
+      </c>
+      <c r="H84">
+        <v>79.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>20.3</v>
+      </c>
+      <c r="K84">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L84">
+        <v>10.7</v>
+      </c>
+      <c r="M84">
+        <v>32.99499600000001</v>
+      </c>
+      <c r="N84">
+        <v>-22.29499600000001</v>
+      </c>
+      <c r="O84">
+        <v>-2.2294996</v>
+      </c>
+      <c r="P84">
+        <v>-20.06549640000001</v>
+      </c>
+      <c r="Q84">
+        <v>-10.46549640000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5608763175346543</v>
+      </c>
+      <c r="T84">
+        <v>6.019481263514418</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03242915986411999</v>
+      </c>
+      <c r="W84">
+        <v>0.2310559166244482</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3242915986411999</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2924235887882853</v>
+      </c>
+      <c r="C85">
+        <v>-67.81235687680127</v>
+      </c>
+      <c r="D85">
+        <v>69.66264312319875</v>
+      </c>
+      <c r="E85">
+        <v>51.15500000000002</v>
+      </c>
+      <c r="F85">
+        <v>139.855</v>
+      </c>
+      <c r="G85">
+        <v>2.38</v>
+      </c>
+      <c r="H85">
+        <v>79.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>20.3</v>
+      </c>
+      <c r="K85">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L85">
+        <v>10.7</v>
+      </c>
+      <c r="M85">
+        <v>33.39737400000001</v>
+      </c>
+      <c r="N85">
+        <v>-22.69737400000001</v>
+      </c>
+      <c r="O85">
+        <v>-2.2697374</v>
+      </c>
+      <c r="P85">
+        <v>-20.42763660000001</v>
+      </c>
+      <c r="Q85">
+        <v>-10.82763660000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.59158668915434</v>
+      </c>
+      <c r="T85">
+        <v>6.373568396662326</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03203844709467276</v>
+      </c>
+      <c r="W85">
+        <v>0.2311492188337922</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3203844709467276</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2944235887882852</v>
+      </c>
+      <c r="C86">
+        <v>-70.04239768037822</v>
+      </c>
+      <c r="D86">
+        <v>69.11760231962178</v>
+      </c>
+      <c r="E86">
+        <v>52.83999999999999</v>
+      </c>
+      <c r="F86">
+        <v>141.54</v>
+      </c>
+      <c r="G86">
+        <v>2.38</v>
+      </c>
+      <c r="H86">
+        <v>79.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>20.3</v>
+      </c>
+      <c r="K86">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L86">
+        <v>10.7</v>
+      </c>
+      <c r="M86">
+        <v>33.799752</v>
+      </c>
+      <c r="N86">
+        <v>-23.099752</v>
+      </c>
+      <c r="O86">
+        <v>-2.309975199999999</v>
+      </c>
+      <c r="P86">
+        <v>-20.7897768</v>
+      </c>
+      <c r="Q86">
+        <v>-11.1897768</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6261358572264859</v>
+      </c>
+      <c r="T86">
+        <v>6.771916421453717</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03165703701021237</v>
+      </c>
+      <c r="W86">
+        <v>0.2312402995619613</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3165703701021239</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2964235887882852</v>
+      </c>
+      <c r="C87">
+        <v>-72.26397589237123</v>
+      </c>
+      <c r="D87">
+        <v>68.58102410762876</v>
+      </c>
+      <c r="E87">
+        <v>54.52499999999999</v>
+      </c>
+      <c r="F87">
+        <v>143.225</v>
+      </c>
+      <c r="G87">
+        <v>2.38</v>
+      </c>
+      <c r="H87">
+        <v>79.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>20.3</v>
+      </c>
+      <c r="K87">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L87">
+        <v>10.7</v>
+      </c>
+      <c r="M87">
+        <v>34.20213</v>
+      </c>
+      <c r="N87">
+        <v>-23.50213</v>
+      </c>
+      <c r="O87">
+        <v>-2.350213</v>
+      </c>
+      <c r="P87">
+        <v>-21.151917</v>
+      </c>
+      <c r="Q87">
+        <v>-11.551917</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6652915810415849</v>
+      </c>
+      <c r="T87">
+        <v>7.223377516217299</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03128460128068046</v>
+      </c>
+      <c r="W87">
+        <v>0.2313292372141735</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3128460128068047</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2984235887882852</v>
+      </c>
+      <c r="C88">
+        <v>-74.47728708649431</v>
+      </c>
+      <c r="D88">
+        <v>68.05271291350569</v>
+      </c>
+      <c r="E88">
+        <v>56.20999999999999</v>
+      </c>
+      <c r="F88">
+        <v>144.91</v>
+      </c>
+      <c r="G88">
+        <v>2.38</v>
+      </c>
+      <c r="H88">
+        <v>79.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>20.3</v>
+      </c>
+      <c r="K88">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L88">
+        <v>10.7</v>
+      </c>
+      <c r="M88">
+        <v>34.604508</v>
+      </c>
+      <c r="N88">
+        <v>-23.904508</v>
+      </c>
+      <c r="O88">
+        <v>-2.3904508</v>
+      </c>
+      <c r="P88">
+        <v>-21.5140572</v>
+      </c>
+      <c r="Q88">
+        <v>-11.9140572</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7100409796874125</v>
+      </c>
+      <c r="T88">
+        <v>7.739333053089963</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03092082684718418</v>
+      </c>
+      <c r="W88">
+        <v>0.2314161065488924</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3092082684718418</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3004235887882852</v>
+      </c>
+      <c r="C89">
+        <v>-76.68252085615319</v>
+      </c>
+      <c r="D89">
+        <v>67.53247914384681</v>
+      </c>
+      <c r="E89">
+        <v>57.895</v>
+      </c>
+      <c r="F89">
+        <v>146.595</v>
+      </c>
+      <c r="G89">
+        <v>2.38</v>
+      </c>
+      <c r="H89">
+        <v>79.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>20.3</v>
+      </c>
+      <c r="K89">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L89">
+        <v>10.7</v>
+      </c>
+      <c r="M89">
+        <v>35.006886</v>
+      </c>
+      <c r="N89">
+        <v>-24.306886</v>
+      </c>
+      <c r="O89">
+        <v>-2.4306886</v>
+      </c>
+      <c r="P89">
+        <v>-21.8761974</v>
+      </c>
+      <c r="Q89">
+        <v>-12.2761974</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7616749012018289</v>
+      </c>
+      <c r="T89">
+        <v>8.334666364866115</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03056541504434298</v>
+      </c>
+      <c r="W89">
+        <v>0.2315009788874109</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3056541504434299</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3024235887882852</v>
+      </c>
+      <c r="C90">
+        <v>-78.87986104129558</v>
+      </c>
+      <c r="D90">
+        <v>67.02013895870442</v>
+      </c>
+      <c r="E90">
+        <v>59.58</v>
+      </c>
+      <c r="F90">
+        <v>148.28</v>
+      </c>
+      <c r="G90">
+        <v>2.38</v>
+      </c>
+      <c r="H90">
+        <v>79.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>20.3</v>
+      </c>
+      <c r="K90">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L90">
+        <v>10.7</v>
+      </c>
+      <c r="M90">
+        <v>35.409264</v>
+      </c>
+      <c r="N90">
+        <v>-24.709264</v>
+      </c>
+      <c r="O90">
+        <v>-2.4709264</v>
+      </c>
+      <c r="P90">
+        <v>-22.2383376</v>
+      </c>
+      <c r="Q90">
+        <v>-12.6383376</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8219144763019814</v>
+      </c>
+      <c r="T90">
+        <v>9.029221895271625</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03021808078247545</v>
+      </c>
+      <c r="W90">
+        <v>0.2315839223091449</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3021808078247545</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3044235887882852</v>
+      </c>
+      <c r="C91">
+        <v>-81.06948594501318</v>
+      </c>
+      <c r="D91">
+        <v>66.51551405498682</v>
+      </c>
+      <c r="E91">
+        <v>61.265</v>
+      </c>
+      <c r="F91">
+        <v>149.965</v>
+      </c>
+      <c r="G91">
+        <v>2.38</v>
+      </c>
+      <c r="H91">
+        <v>79.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>20.3</v>
+      </c>
+      <c r="K91">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L91">
+        <v>10.7</v>
+      </c>
+      <c r="M91">
+        <v>35.81164200000001</v>
+      </c>
+      <c r="N91">
+        <v>-25.11164200000001</v>
+      </c>
+      <c r="O91">
+        <v>-2.5111642</v>
+      </c>
+      <c r="P91">
+        <v>-22.60047780000001</v>
+      </c>
+      <c r="Q91">
+        <v>-13.00047780000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8931067014203433</v>
+      </c>
+      <c r="T91">
+        <v>9.850060249387228</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02987855178491954</v>
+      </c>
+      <c r="W91">
+        <v>0.2316650018337612</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2987855178491955</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3064235887882852</v>
+      </c>
+      <c r="C92">
+        <v>-83.25156854043124</v>
+      </c>
+      <c r="D92">
+        <v>66.01843145956877</v>
+      </c>
+      <c r="E92">
+        <v>62.95</v>
+      </c>
+      <c r="F92">
+        <v>151.65</v>
+      </c>
+      <c r="G92">
+        <v>2.38</v>
+      </c>
+      <c r="H92">
+        <v>79.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>20.3</v>
+      </c>
+      <c r="K92">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L92">
+        <v>10.7</v>
+      </c>
+      <c r="M92">
+        <v>36.21402</v>
+      </c>
+      <c r="N92">
+        <v>-25.51402000000001</v>
+      </c>
+      <c r="O92">
+        <v>-2.551402</v>
+      </c>
+      <c r="P92">
+        <v>-22.96261800000001</v>
+      </c>
+      <c r="Q92">
+        <v>-13.362618</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9785373715623777</v>
+      </c>
+      <c r="T92">
+        <v>10.83506627432595</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02954656787619821</v>
+      </c>
+      <c r="W92">
+        <v>0.2317442795911639</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2954656787619822</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3084235887882852</v>
+      </c>
+      <c r="C93">
+        <v>-85.42627666839039</v>
+      </c>
+      <c r="D93">
+        <v>65.52872333160963</v>
+      </c>
+      <c r="E93">
+        <v>64.63500000000001</v>
+      </c>
+      <c r="F93">
+        <v>153.335</v>
+      </c>
+      <c r="G93">
+        <v>2.38</v>
+      </c>
+      <c r="H93">
+        <v>79.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>20.3</v>
+      </c>
+      <c r="K93">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L93">
+        <v>10.7</v>
+      </c>
+      <c r="M93">
+        <v>36.616398</v>
+      </c>
+      <c r="N93">
+        <v>-25.916398</v>
+      </c>
+      <c r="O93">
+        <v>-2.5916398</v>
+      </c>
+      <c r="P93">
+        <v>-23.32475820000001</v>
+      </c>
+      <c r="Q93">
+        <v>-13.7247582</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.082952635069309</v>
+      </c>
+      <c r="T93">
+        <v>12.03896252702884</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02922188031711911</v>
+      </c>
+      <c r="W93">
+        <v>0.231821814980272</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2922188031711912</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3104235887882852</v>
+      </c>
+      <c r="C94">
+        <v>-87.59377322639503</v>
+      </c>
+      <c r="D94">
+        <v>65.04622677360499</v>
+      </c>
+      <c r="E94">
+        <v>66.32000000000001</v>
+      </c>
+      <c r="F94">
+        <v>155.02</v>
+      </c>
+      <c r="G94">
+        <v>2.38</v>
+      </c>
+      <c r="H94">
+        <v>79.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>20.3</v>
+      </c>
+      <c r="K94">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L94">
+        <v>10.7</v>
+      </c>
+      <c r="M94">
+        <v>37.018776</v>
+      </c>
+      <c r="N94">
+        <v>-26.318776</v>
+      </c>
+      <c r="O94">
+        <v>-2.6318776</v>
+      </c>
+      <c r="P94">
+        <v>-23.6868984</v>
+      </c>
+      <c r="Q94">
+        <v>-14.0868984</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.213471714452973</v>
+      </c>
+      <c r="T94">
+        <v>13.54383284290745</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02890425118323738</v>
+      </c>
+      <c r="W94">
+        <v>0.2318976648174429</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2890425118323738</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3124235887882852</v>
+      </c>
+      <c r="C95">
+        <v>-89.75421634927531</v>
+      </c>
+      <c r="D95">
+        <v>64.57078365072471</v>
+      </c>
+      <c r="E95">
+        <v>68.00500000000001</v>
+      </c>
+      <c r="F95">
+        <v>156.705</v>
+      </c>
+      <c r="G95">
+        <v>2.38</v>
+      </c>
+      <c r="H95">
+        <v>79.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>20.3</v>
+      </c>
+      <c r="K95">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L95">
+        <v>10.7</v>
+      </c>
+      <c r="M95">
+        <v>37.421154</v>
+      </c>
+      <c r="N95">
+        <v>-26.721154</v>
+      </c>
+      <c r="O95">
+        <v>-2.6721154</v>
+      </c>
+      <c r="P95">
+        <v>-24.0490386</v>
+      </c>
+      <c r="Q95">
+        <v>-14.4490386</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.381281959374826</v>
+      </c>
+      <c r="T95">
+        <v>15.47866610617994</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02859345278341763</v>
+      </c>
+      <c r="W95">
+        <v>0.2319718834753199</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2859345278341763</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3144235887882852</v>
+      </c>
+      <c r="C96">
+        <v>-91.90775958198333</v>
+      </c>
+      <c r="D96">
+        <v>64.10224041801669</v>
+      </c>
+      <c r="E96">
+        <v>69.69000000000001</v>
+      </c>
+      <c r="F96">
+        <v>158.39</v>
+      </c>
+      <c r="G96">
+        <v>2.38</v>
+      </c>
+      <c r="H96">
+        <v>79.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>20.3</v>
+      </c>
+      <c r="K96">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L96">
+        <v>10.7</v>
+      </c>
+      <c r="M96">
+        <v>37.82353200000001</v>
+      </c>
+      <c r="N96">
+        <v>-27.12353200000001</v>
+      </c>
+      <c r="O96">
+        <v>-2.7123532</v>
+      </c>
+      <c r="P96">
+        <v>-24.41117880000001</v>
+      </c>
+      <c r="Q96">
+        <v>-14.81117880000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.605028952603964</v>
+      </c>
+      <c r="T96">
+        <v>18.05844379054327</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02828926711550893</v>
+      </c>
+      <c r="W96">
+        <v>0.2320445230128165</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2828926711550893</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3164235887882852</v>
+      </c>
+      <c r="C97">
+        <v>-94.05455204492064</v>
+      </c>
+      <c r="D97">
+        <v>63.64044795507938</v>
+      </c>
+      <c r="E97">
+        <v>71.37500000000001</v>
+      </c>
+      <c r="F97">
+        <v>160.075</v>
+      </c>
+      <c r="G97">
+        <v>2.38</v>
+      </c>
+      <c r="H97">
+        <v>79.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>20.3</v>
+      </c>
+      <c r="K97">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L97">
+        <v>10.7</v>
+      </c>
+      <c r="M97">
+        <v>38.22591000000001</v>
+      </c>
+      <c r="N97">
+        <v>-27.52591000000001</v>
+      </c>
+      <c r="O97">
+        <v>-2.752591</v>
+      </c>
+      <c r="P97">
+        <v>-24.77331900000001</v>
+      </c>
+      <c r="Q97">
+        <v>-15.17331900000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.918274743124758</v>
+      </c>
+      <c r="T97">
+        <v>21.67013254865193</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0279914853563983</v>
+      </c>
+      <c r="W97">
+        <v>0.2321156332968921</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2799148535639832</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3184235887882853</v>
+      </c>
+      <c r="C98">
+        <v>-96.19473859217048</v>
+      </c>
+      <c r="D98">
+        <v>63.18526140782951</v>
+      </c>
+      <c r="E98">
+        <v>73.05999999999999</v>
+      </c>
+      <c r="F98">
+        <v>161.76</v>
+      </c>
+      <c r="G98">
+        <v>2.38</v>
+      </c>
+      <c r="H98">
+        <v>79.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>20.3</v>
+      </c>
+      <c r="K98">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L98">
+        <v>10.7</v>
+      </c>
+      <c r="M98">
+        <v>38.628288</v>
+      </c>
+      <c r="N98">
+        <v>-27.928288</v>
+      </c>
+      <c r="O98">
+        <v>-2.792828799999999</v>
+      </c>
+      <c r="P98">
+        <v>-25.1354592</v>
+      </c>
+      <c r="Q98">
+        <v>-15.5354592</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.388143428905942</v>
+      </c>
+      <c r="T98">
+        <v>27.08766568581485</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02769990738393583</v>
+      </c>
+      <c r="W98">
+        <v>0.2321852621167161</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2769990738393584</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3204235887882853</v>
+      </c>
+      <c r="C99">
+        <v>-98.32845996298812</v>
+      </c>
+      <c r="D99">
+        <v>62.73654003701188</v>
+      </c>
+      <c r="E99">
+        <v>74.74499999999999</v>
+      </c>
+      <c r="F99">
+        <v>163.445</v>
+      </c>
+      <c r="G99">
+        <v>2.38</v>
+      </c>
+      <c r="H99">
+        <v>79.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>20.3</v>
+      </c>
+      <c r="K99">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L99">
+        <v>10.7</v>
+      </c>
+      <c r="M99">
+        <v>39.030666</v>
+      </c>
+      <c r="N99">
+        <v>-28.330666</v>
+      </c>
+      <c r="O99">
+        <v>-2.8330666</v>
+      </c>
+      <c r="P99">
+        <v>-25.49759940000001</v>
+      </c>
+      <c r="Q99">
+        <v>-15.8975994</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.171257905207923</v>
+      </c>
+      <c r="T99">
+        <v>36.11688758108647</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02741434132843133</v>
+      </c>
+      <c r="W99">
+        <v>0.2322534552907706</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2741434132843134</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3224235887882853</v>
+      </c>
+      <c r="C100">
+        <v>-100.4558529268811</v>
+      </c>
+      <c r="D100">
+        <v>62.29414707311886</v>
+      </c>
+      <c r="E100">
+        <v>76.42999999999999</v>
+      </c>
+      <c r="F100">
+        <v>165.13</v>
+      </c>
+      <c r="G100">
+        <v>2.38</v>
+      </c>
+      <c r="H100">
+        <v>79.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>20.3</v>
+      </c>
+      <c r="K100">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L100">
+        <v>10.7</v>
+      </c>
+      <c r="M100">
+        <v>39.433044</v>
+      </c>
+      <c r="N100">
+        <v>-28.733044</v>
+      </c>
+      <c r="O100">
+        <v>-2.8733044</v>
+      </c>
+      <c r="P100">
+        <v>-25.8597396</v>
+      </c>
+      <c r="Q100">
+        <v>-16.2597396</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.737486857811884</v>
+      </c>
+      <c r="T100">
+        <v>54.1753313716297</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0271346031516106</v>
+      </c>
+      <c r="W100">
+        <v>0.2323202567673954</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2713460315161061</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3244235887882853</v>
+      </c>
+      <c r="C101">
+        <v>-102.5770504225949</v>
+      </c>
+      <c r="D101">
+        <v>61.85794957740506</v>
+      </c>
+      <c r="E101">
+        <v>78.11499999999999</v>
+      </c>
+      <c r="F101">
+        <v>166.815</v>
+      </c>
+      <c r="G101">
+        <v>2.38</v>
+      </c>
+      <c r="H101">
+        <v>79.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>20.3</v>
+      </c>
+      <c r="K101">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L101">
+        <v>10.7</v>
+      </c>
+      <c r="M101">
+        <v>39.835422</v>
+      </c>
+      <c r="N101">
+        <v>-29.135422</v>
+      </c>
+      <c r="O101">
+        <v>-2.9135422</v>
+      </c>
+      <c r="P101">
+        <v>-26.2218798</v>
+      </c>
+      <c r="Q101">
+        <v>-16.6218798</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.436173715623768</v>
+      </c>
+      <c r="T101">
+        <v>108.3506627432594</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02686051625108928</v>
+      </c>
+      <c r="W101">
+        <v>0.2323857087192399</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2686051625108929</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
